--- a/limerick_pipeline/supply/Limerick_Housing_Supply_Dashboard.xlsx
+++ b/limerick_pipeline/supply/Limerick_Housing_Supply_Dashboard.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Assumptions" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Schemes!$A$1:$AC$264</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Schemes!$A$1:$AC$266</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Sites!$A$1:$U$134</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5883" uniqueCount="1896">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5923" uniqueCount="1912">
   <si>
     <t xml:space="preserve">Limerick housing supply – audit land, consents and expected delivery</t>
   </si>
@@ -259,7 +259,7 @@
     <t xml:space="preserve">• 4,064 units are under construction. These are the most reliable part of the next two years.</t>
   </si>
   <si>
-    <t xml:space="preserve">• 4,981 units have a live permission but no start. 1,417 of them are past the usual time to start or close to expiry, so they are rated low confidence.</t>
+    <t xml:space="preserve">• 5,005 units have a live permission but no start. 1,441 of them are past the usual time to start or close to expiry, so they are rated low confidence.</t>
   </si>
   <si>
     <t xml:space="preserve">• Public bodies (council, AHBs, LDA) hold 15% of consented units.</t>
@@ -4468,6 +4468,27 @@
     <t xml:space="preserve">2030-03-11</t>
   </si>
   <si>
+    <t xml:space="preserve">REG-20525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Register: the construction of 14 dwelling houses, including 2 no semi-detached 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Croom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-12-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-12-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Permitted 2021-12, past typical start date with no commencement: start assumed in 9 months; expiry falls before assumed start</t>
+  </si>
+  <si>
     <t xml:space="preserve">1223809</t>
   </si>
   <si>
@@ -4552,6 +4573,21 @@
     <t xml:space="preserve">2031-02-25</t>
   </si>
   <si>
+    <t xml:space="preserve">REG-24151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Register: the construction of 10 dwelling units to include 2 no. detached 5 bedr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-01-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2030-01-14</t>
+  </si>
+  <si>
     <t xml:space="preserve">1164066</t>
   </si>
   <si>
@@ -5545,7 +5581,7 @@
     <t xml:space="preserve">2031+ left at zero: the allowance is a yearly rate, and the tracker’s 2031+ column is the tail of known schemes.</t>
   </si>
   <si>
-    <t xml:space="preserve">Register grants of 10+ units since 2021 not found in the tracker (check list)</t>
+    <t xml:space="preserve">Register grants of 10+ units since 2021 not in CIS: checked 08/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Description</t>
@@ -5563,6 +5599,9 @@
     <t xml:space="preserve">Address</t>
   </si>
   <si>
+    <t xml:space="preserve">Finding</t>
+  </si>
+  <si>
     <t xml:space="preserve">a residential development comprising 96 no. residential units, (2 no. detached houses; 16 no. semi-detached houses; 40 no. terrace units and 38 no. in 2 no. fou</t>
   </si>
   <si>
@@ -5575,6 +5614,9 @@
     <t xml:space="preserve">Baunacloka , Raheen , Co. Limerick</t>
   </si>
   <si>
+    <t xml:space="preserve">Refused on appeal, PL91.317106 (20/10/2025). Not live.</t>
+  </si>
+  <si>
     <t xml:space="preserve">the construction of 40 No. residential units comprising of 20 No. Houses and 20 No. Apartments, all two-storey in height. The units proposed are a mix of 1 and </t>
   </si>
   <si>
@@ -5587,6 +5629,9 @@
     <t xml:space="preserve">Saint Ita's Road , Abbeyfeale West , Abbeyfeale</t>
   </si>
   <si>
+    <t xml:space="preserve">Refused on appeal, PL91.322380 (20/08/2025). Not live.</t>
+  </si>
+  <si>
     <t xml:space="preserve">change of use from Medical Centre previously granted under permission ref. 19/710 to 19no. student spaces of 507.6sqm on ground floor.  Provision of 12no. car p</t>
   </si>
   <si>
@@ -5599,31 +5644,34 @@
     <t xml:space="preserve">Hassett's Cross , Limerick.</t>
   </si>
   <si>
+    <t xml:space="preserve">Change of use within 19/710 (Hassett’s Cross, already tracked); expired 14/03/2026. Not new supply.</t>
+  </si>
+  <si>
     <t xml:space="preserve">the construction of 14 dwelling houses, including 2 no semi-detached 2 bedroom bungalows, 12 no 2 storey semi-detached 3 bedroom houses, of which 4 will have an</t>
   </si>
   <si>
-    <t xml:space="preserve">20525</t>
-  </si>
-  <si>
     <t xml:space="preserve">16/03/2021</t>
   </si>
   <si>
     <t xml:space="preserve">Skagh , Croom , Co. Limerick</t>
   </si>
   <si>
+    <t xml:space="preserve">Added to tracker. Granted on appeal PL91.309917 (02/12/2021); expires 01/12/2026; no commencement notice.</t>
+  </si>
+  <si>
     <t xml:space="preserve">the construction of 10 dwelling units to include 2 no. detached 5 bedroom bungalow dwellings &amp; 8 no. 3 bed semi-detached dwellings, all necessary ancillary site</t>
   </si>
   <si>
-    <t xml:space="preserve">24151</t>
-  </si>
-  <si>
     <t xml:space="preserve">04/12/2024</t>
   </si>
   <si>
     <t xml:space="preserve">Cois Sruthain , Croom , Co. Limerick</t>
   </si>
   <si>
-    <t xml:space="preserve">Not added to the tracker: each needs checking (live, expired, superseded, or already counted under another reference).</t>
+    <t xml:space="preserve">Added to tracker. Granted 15/01/2025; expires 14/01/2030; no commencement notice.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two live schemes (Croom, 24 homes) added to the tracker as register-only records. The others are refused or not new supply.</t>
   </si>
   <si>
     <t xml:space="preserve">Method and assumptions</t>
@@ -6259,10 +6307,10 @@
                   <c:v>2037.6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1401.6</c:v>
+                  <c:v>1415.7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1717.3</c:v>
+                  <c:v>1727.2</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>721.1</c:v>
@@ -6692,11 +6740,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="59128457"/>
-        <c:axId val="33804873"/>
+        <c:axId val="78628746"/>
+        <c:axId val="49142908"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="59128457"/>
+        <c:axId val="78628746"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6728,7 +6776,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33804873"/>
+        <c:crossAx val="49142908"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6736,7 +6784,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="33804873"/>
+        <c:axId val="49142908"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -6803,7 +6851,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59128457"/>
+        <c:crossAx val="78628746"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7135,7 +7183,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$F$2:$F$264,"Audit land – within site",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$F$2:$F$266,"Audit land – within site",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>5208</v>
       </c>
     </row>
@@ -7162,7 +7210,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$F$2:$F$264,"Audit land – edge (check)",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$F$2:$F$266,"Audit land – edge (check)",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>478</v>
       </c>
     </row>
@@ -7171,7 +7219,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$F$2:$F$264,"City – outside audit land",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$F$2:$F$266,"City – outside audit land",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>2845</v>
       </c>
     </row>
@@ -7180,8 +7228,8 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$F$2:$F$264,"County – audit not yet supplied",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
-        <v>1945</v>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$F$2:$F$266,"County – audit not yet supplied",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
+        <v>1969</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7190,7 +7238,7 @@
       </c>
       <c r="B14" s="7" t="n">
         <f aca="false">B8+B11+B12+B13</f>
-        <v>10476</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7198,7 +7246,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="n">
-        <f aca="false">SUMIFS(Schemes!$N$2:$N$264,Schemes!$I$2:$I$264,"Student (PBSA)",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$N$2:$N$266,Schemes!$I$2:$I$266,"Student (PBSA)",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>2142</v>
       </c>
     </row>
@@ -7207,8 +7255,8 @@
         <v>15</v>
       </c>
       <c r="B16" s="7" t="n">
-        <f aca="false">SUM(Schemes!$W$2:$W$264)+SUM(Schemes!$X$2:$X$264)+SUM(Schemes!$Y$2:$Y$264)+SUM(Schemes!$Z$2:$Z$264)+SUM(Schemes!$AA$2:$AA$264)</f>
-        <v>7471.8</v>
+        <f aca="false">SUM(Schemes!$W$2:$W$266)+SUM(Schemes!$X$2:$X$266)+SUM(Schemes!$Y$2:$Y$266)+SUM(Schemes!$Z$2:$Z$266)+SUM(Schemes!$AA$2:$AA$266)</f>
+        <v>7495.8</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7480,19 +7528,19 @@
         <v>41</v>
       </c>
       <c r="B30" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$F$2:$F$264,$A30,Schemes!$K$2:$K$264,"Complete")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$F$2:$F$266,$A30,Schemes!$K$2:$K$266,"Complete")</f>
         <v>76</v>
       </c>
       <c r="C30" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$F$2:$F$264,$A30,Schemes!$K$2:$K$264,"Under construction")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$F$2:$F$266,$A30,Schemes!$K$2:$K$266,"Under construction")</f>
         <v>1603</v>
       </c>
       <c r="D30" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$F$2:$F$264,$A30,Schemes!$K$2:$K$264,"Not started – permission live")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$F$2:$F$266,$A30,Schemes!$K$2:$K$266,"Not started – permission live")</f>
         <v>3498</v>
       </c>
       <c r="E30" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$F$2:$F$264,$A30,Schemes!$K$2:$K$264,"Stalled (CIS)")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$F$2:$F$266,$A30,Schemes!$K$2:$K$266,"Stalled (CIS)")</f>
         <v>31</v>
       </c>
       <c r="F30" s="17" t="n">
@@ -7500,11 +7548,11 @@
         <v>5208</v>
       </c>
       <c r="G30" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$F$2:$F$264,$A30,Schemes!$K$2:$K$264,"Not started – past expiry")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$F$2:$F$266,$A30,Schemes!$K$2:$K$266,"Not started – past expiry")</f>
         <v>149</v>
       </c>
       <c r="H30" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$F$2:$F$264,$A30,Schemes!$K$2:$K$264,"In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$F$2:$F$266,$A30,Schemes!$K$2:$K$266,"In planning")</f>
         <v>97</v>
       </c>
     </row>
@@ -7513,19 +7561,19 @@
         <v>42</v>
       </c>
       <c r="B31" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$F$2:$F$264,$A31,Schemes!$K$2:$K$264,"Complete")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$F$2:$F$266,$A31,Schemes!$K$2:$K$266,"Complete")</f>
         <v>80</v>
       </c>
       <c r="C31" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$F$2:$F$264,$A31,Schemes!$K$2:$K$264,"Under construction")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$F$2:$F$266,$A31,Schemes!$K$2:$K$266,"Under construction")</f>
         <v>218</v>
       </c>
       <c r="D31" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$F$2:$F$264,$A31,Schemes!$K$2:$K$264,"Not started – permission live")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$F$2:$F$266,$A31,Schemes!$K$2:$K$266,"Not started – permission live")</f>
         <v>180</v>
       </c>
       <c r="E31" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$F$2:$F$264,$A31,Schemes!$K$2:$K$264,"Stalled (CIS)")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$F$2:$F$266,$A31,Schemes!$K$2:$K$266,"Stalled (CIS)")</f>
         <v>0</v>
       </c>
       <c r="F31" s="17" t="n">
@@ -7533,11 +7581,11 @@
         <v>478</v>
       </c>
       <c r="G31" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$F$2:$F$264,$A31,Schemes!$K$2:$K$264,"Not started – past expiry")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$F$2:$F$266,$A31,Schemes!$K$2:$K$266,"Not started – past expiry")</f>
         <v>0</v>
       </c>
       <c r="H31" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$F$2:$F$264,$A31,Schemes!$K$2:$K$264,"In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$F$2:$F$266,$A31,Schemes!$K$2:$K$266,"In planning")</f>
         <v>4</v>
       </c>
     </row>
@@ -7546,19 +7594,19 @@
         <v>43</v>
       </c>
       <c r="B32" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$F$2:$F$264,$A32,Schemes!$K$2:$K$264,"Complete")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$F$2:$F$266,$A32,Schemes!$K$2:$K$266,"Complete")</f>
         <v>971</v>
       </c>
       <c r="C32" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$F$2:$F$264,$A32,Schemes!$K$2:$K$264,"Under construction")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$F$2:$F$266,$A32,Schemes!$K$2:$K$266,"Under construction")</f>
         <v>1342</v>
       </c>
       <c r="D32" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$F$2:$F$264,$A32,Schemes!$K$2:$K$264,"Not started – permission live")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$F$2:$F$266,$A32,Schemes!$K$2:$K$266,"Not started – permission live")</f>
         <v>532</v>
       </c>
       <c r="E32" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$F$2:$F$264,$A32,Schemes!$K$2:$K$264,"Stalled (CIS)")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$F$2:$F$266,$A32,Schemes!$K$2:$K$266,"Stalled (CIS)")</f>
         <v>0</v>
       </c>
       <c r="F32" s="17" t="n">
@@ -7566,11 +7614,11 @@
         <v>2845</v>
       </c>
       <c r="G32" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$F$2:$F$264,$A32,Schemes!$K$2:$K$264,"Not started – past expiry")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$F$2:$F$266,$A32,Schemes!$K$2:$K$266,"Not started – past expiry")</f>
         <v>71</v>
       </c>
       <c r="H32" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$F$2:$F$264,$A32,Schemes!$K$2:$K$264,"In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$F$2:$F$266,$A32,Schemes!$K$2:$K$266,"In planning")</f>
         <v>72</v>
       </c>
     </row>
@@ -7579,31 +7627,31 @@
         <v>44</v>
       </c>
       <c r="B33" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$F$2:$F$264,$A33,Schemes!$K$2:$K$264,"Complete")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$F$2:$F$266,$A33,Schemes!$K$2:$K$266,"Complete")</f>
         <v>148</v>
       </c>
       <c r="C33" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$F$2:$F$264,$A33,Schemes!$K$2:$K$264,"Under construction")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$F$2:$F$266,$A33,Schemes!$K$2:$K$266,"Under construction")</f>
         <v>901</v>
       </c>
       <c r="D33" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$F$2:$F$264,$A33,Schemes!$K$2:$K$264,"Not started – permission live")</f>
-        <v>771</v>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$F$2:$F$266,$A33,Schemes!$K$2:$K$266,"Not started – permission live")</f>
+        <v>795</v>
       </c>
       <c r="E33" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$F$2:$F$264,$A33,Schemes!$K$2:$K$264,"Stalled (CIS)")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$F$2:$F$266,$A33,Schemes!$K$2:$K$266,"Stalled (CIS)")</f>
         <v>125</v>
       </c>
       <c r="F33" s="17" t="n">
         <f aca="false">SUM(B33:E33)</f>
-        <v>1945</v>
+        <v>1969</v>
       </c>
       <c r="G33" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$F$2:$F$264,$A33,Schemes!$K$2:$K$264,"Not started – past expiry")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$F$2:$F$266,$A33,Schemes!$K$2:$K$266,"Not started – past expiry")</f>
         <v>91</v>
       </c>
       <c r="H33" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$F$2:$F$264,$A33,Schemes!$K$2:$K$264,"In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$F$2:$F$266,$A33,Schemes!$K$2:$K$266,"In planning")</f>
         <v>90</v>
       </c>
     </row>
@@ -7621,7 +7669,7 @@
       </c>
       <c r="D34" s="15" t="n">
         <f aca="false">SUM(D30:D33)</f>
-        <v>4981</v>
+        <v>5005</v>
       </c>
       <c r="E34" s="15" t="n">
         <f aca="false">SUM(E30:E33)</f>
@@ -7629,7 +7677,7 @@
       </c>
       <c r="F34" s="15" t="n">
         <f aca="false">SUM(F30:F33)</f>
-        <v>10476</v>
+        <v>10500</v>
       </c>
       <c r="G34" s="15" t="n">
         <f aca="false">SUM(G30:G33)</f>
@@ -7673,28 +7721,28 @@
         <v>29</v>
       </c>
       <c r="B38" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A38,Schemes!$F$2:$F$264,"Audit land – within site",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A38,Schemes!$F$2:$F$266,"Audit land – within site",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>4481</v>
       </c>
       <c r="C38" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A38,Schemes!$F$2:$F$264,"Audit land – edge (check)",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A38,Schemes!$F$2:$F$266,"Audit land – edge (check)",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>393</v>
       </c>
       <c r="D38" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A38,Schemes!$F$2:$F$264,"City – outside audit land",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A38,Schemes!$F$2:$F$266,"City – outside audit land",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>2499</v>
       </c>
       <c r="E38" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A38,Schemes!$F$2:$F$264,"County – audit not yet supplied",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
-        <v>1549</v>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A38,Schemes!$F$2:$F$266,"County – audit not yet supplied",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
+        <v>1573</v>
       </c>
       <c r="F38" s="17" t="n">
         <f aca="false">SUM(B38:E38)</f>
-        <v>8922</v>
+        <v>8946</v>
       </c>
       <c r="G38" s="18" t="n">
         <f aca="false">IF($F$42=0,0,F38/$F$42)</f>
-        <v>0.851660939289805</v>
+        <v>0.852</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7702,19 +7750,19 @@
         <v>50</v>
       </c>
       <c r="B39" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A39,Schemes!$F$2:$F$264,"Audit land – within site",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A39,Schemes!$F$2:$F$266,"Audit land – within site",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>297</v>
       </c>
       <c r="C39" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A39,Schemes!$F$2:$F$264,"Audit land – edge (check)",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A39,Schemes!$F$2:$F$266,"Audit land – edge (check)",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>81</v>
       </c>
       <c r="D39" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A39,Schemes!$F$2:$F$264,"City – outside audit land",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A39,Schemes!$F$2:$F$266,"City – outside audit land",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>268</v>
       </c>
       <c r="E39" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A39,Schemes!$F$2:$F$264,"County – audit not yet supplied",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A39,Schemes!$F$2:$F$266,"County – audit not yet supplied",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>325</v>
       </c>
       <c r="F39" s="17" t="n">
@@ -7723,7 +7771,7 @@
       </c>
       <c r="G39" s="18" t="n">
         <f aca="false">IF($F$42=0,0,F39/$F$42)</f>
-        <v>0.0926880488736159</v>
+        <v>0.0924761904761905</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7731,19 +7779,19 @@
         <v>51</v>
       </c>
       <c r="B40" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A40,Schemes!$F$2:$F$264,"Audit land – within site",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A40,Schemes!$F$2:$F$266,"Audit land – within site",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>145</v>
       </c>
       <c r="C40" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A40,Schemes!$F$2:$F$264,"Audit land – edge (check)",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A40,Schemes!$F$2:$F$266,"Audit land – edge (check)",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>4</v>
       </c>
       <c r="D40" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A40,Schemes!$F$2:$F$264,"City – outside audit land",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A40,Schemes!$F$2:$F$266,"City – outside audit land",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>78</v>
       </c>
       <c r="E40" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A40,Schemes!$F$2:$F$264,"County – audit not yet supplied",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A40,Schemes!$F$2:$F$266,"County – audit not yet supplied",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>71</v>
       </c>
       <c r="F40" s="17" t="n">
@@ -7752,7 +7800,7 @@
       </c>
       <c r="G40" s="18" t="n">
         <f aca="false">IF($F$42=0,0,F40/$F$42)</f>
-        <v>0.0284459717449408</v>
+        <v>0.0283809523809524</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7760,19 +7808,19 @@
         <v>52</v>
       </c>
       <c r="B41" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A41,Schemes!$F$2:$F$264,"Audit land – within site",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A41,Schemes!$F$2:$F$266,"Audit land – within site",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>285</v>
       </c>
       <c r="C41" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A41,Schemes!$F$2:$F$264,"Audit land – edge (check)",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A41,Schemes!$F$2:$F$266,"Audit land – edge (check)",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>0</v>
       </c>
       <c r="D41" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A41,Schemes!$F$2:$F$264,"City – outside audit land",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A41,Schemes!$F$2:$F$266,"City – outside audit land",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>0</v>
       </c>
       <c r="E41" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A41,Schemes!$F$2:$F$264,"County – audit not yet supplied",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A41,Schemes!$F$2:$F$266,"County – audit not yet supplied",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>0</v>
       </c>
       <c r="F41" s="17" t="n">
@@ -7781,7 +7829,7 @@
       </c>
       <c r="G41" s="18" t="n">
         <f aca="false">IF($F$42=0,0,F41/$F$42)</f>
-        <v>0.027205040091638</v>
+        <v>0.0271428571428571</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7802,11 +7850,11 @@
       </c>
       <c r="E42" s="15" t="n">
         <f aca="false">SUM(E38:E41)</f>
-        <v>1945</v>
+        <v>1969</v>
       </c>
       <c r="F42" s="15" t="n">
         <f aca="false">SUM(F38:F41)</f>
-        <v>10476</v>
+        <v>10500</v>
       </c>
       <c r="G42" s="19" t="n">
         <f aca="false">IF($F$42=0,0,F42/$F$42)</f>
@@ -7839,7 +7887,7 @@
       </c>
       <c r="G43" s="21" t="n">
         <f aca="false">IF($F$42=0,0,F43/$F$42)</f>
-        <v>0.148339060710195</v>
+        <v>0.148</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7881,35 +7929,35 @@
         <v>29</v>
       </c>
       <c r="B47" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$W$2:$W$264,Schemes!$H$2:$H$264,$A47)</f>
+        <f aca="false">SUMIFS(Schemes!$W$2:$W$266,Schemes!$H$2:$H$266,$A47)</f>
         <v>528.4</v>
       </c>
       <c r="C47" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$X$2:$X$264,Schemes!$H$2:$H$264,$A47)</f>
+        <f aca="false">SUMIFS(Schemes!$X$2:$X$266,Schemes!$H$2:$H$266,$A47)</f>
         <v>2037.6</v>
       </c>
       <c r="D47" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$Y$2:$Y$264,Schemes!$H$2:$H$264,$A47)</f>
-        <v>1401.6</v>
+        <f aca="false">SUMIFS(Schemes!$Y$2:$Y$266,Schemes!$H$2:$H$266,$A47)</f>
+        <v>1415.7</v>
       </c>
       <c r="E47" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$Z$2:$Z$264,Schemes!$H$2:$H$264,$A47)</f>
-        <v>1717.3</v>
+        <f aca="false">SUMIFS(Schemes!$Z$2:$Z$266,Schemes!$H$2:$H$266,$A47)</f>
+        <v>1727.2</v>
       </c>
       <c r="F47" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$AA$2:$AA$264,Schemes!$H$2:$H$264,$A47)</f>
+        <f aca="false">SUMIFS(Schemes!$AA$2:$AA$266,Schemes!$H$2:$H$266,$A47)</f>
         <v>721.1</v>
       </c>
       <c r="G47" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$AB$2:$AB$264,Schemes!$H$2:$H$264,$A47)</f>
+        <f aca="false">SUMIFS(Schemes!$AB$2:$AB$266,Schemes!$H$2:$H$266,$A47)</f>
         <v>1386</v>
       </c>
       <c r="H47" s="17" t="n">
         <f aca="false">SUM(B47:G47)</f>
-        <v>7792</v>
+        <v>7816</v>
       </c>
       <c r="I47" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$AC$2:$AC$264,Schemes!$H$2:$H$264,$A47)</f>
+        <f aca="false">SUMIFS(Schemes!$AC$2:$AC$266,Schemes!$H$2:$H$266,$A47)</f>
         <v>516</v>
       </c>
     </row>
@@ -7918,27 +7966,27 @@
         <v>50</v>
       </c>
       <c r="B48" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$W$2:$W$264,Schemes!$H$2:$H$264,$A48)</f>
+        <f aca="false">SUMIFS(Schemes!$W$2:$W$266,Schemes!$H$2:$H$266,$A48)</f>
         <v>49.1</v>
       </c>
       <c r="C48" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$X$2:$X$264,Schemes!$H$2:$H$264,$A48)</f>
+        <f aca="false">SUMIFS(Schemes!$X$2:$X$266,Schemes!$H$2:$H$266,$A48)</f>
         <v>225.6</v>
       </c>
       <c r="D48" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$Y$2:$Y$264,Schemes!$H$2:$H$264,$A48)</f>
+        <f aca="false">SUMIFS(Schemes!$Y$2:$Y$266,Schemes!$H$2:$H$266,$A48)</f>
         <v>224.6</v>
       </c>
       <c r="E48" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$Z$2:$Z$264,Schemes!$H$2:$H$264,$A48)</f>
+        <f aca="false">SUMIFS(Schemes!$Z$2:$Z$266,Schemes!$H$2:$H$266,$A48)</f>
         <v>162.1</v>
       </c>
       <c r="F48" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$AA$2:$AA$264,Schemes!$H$2:$H$264,$A48)</f>
+        <f aca="false">SUMIFS(Schemes!$AA$2:$AA$266,Schemes!$H$2:$H$266,$A48)</f>
         <v>68.2</v>
       </c>
       <c r="G48" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$AB$2:$AB$264,Schemes!$H$2:$H$264,$A48)</f>
+        <f aca="false">SUMIFS(Schemes!$AB$2:$AB$266,Schemes!$H$2:$H$266,$A48)</f>
         <v>34.4</v>
       </c>
       <c r="H48" s="17" t="n">
@@ -7946,7 +7994,7 @@
         <v>764</v>
       </c>
       <c r="I48" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$AC$2:$AC$264,Schemes!$H$2:$H$264,$A48)</f>
+        <f aca="false">SUMIFS(Schemes!$AC$2:$AC$266,Schemes!$H$2:$H$266,$A48)</f>
         <v>173</v>
       </c>
     </row>
@@ -7955,27 +8003,27 @@
         <v>51</v>
       </c>
       <c r="B49" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$W$2:$W$264,Schemes!$H$2:$H$264,$A49)</f>
+        <f aca="false">SUMIFS(Schemes!$W$2:$W$266,Schemes!$H$2:$H$266,$A49)</f>
         <v>10.9</v>
       </c>
       <c r="C49" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$X$2:$X$264,Schemes!$H$2:$H$264,$A49)</f>
+        <f aca="false">SUMIFS(Schemes!$X$2:$X$266,Schemes!$H$2:$H$266,$A49)</f>
         <v>92.3</v>
       </c>
       <c r="D49" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$Y$2:$Y$264,Schemes!$H$2:$H$264,$A49)</f>
+        <f aca="false">SUMIFS(Schemes!$Y$2:$Y$266,Schemes!$H$2:$H$266,$A49)</f>
         <v>84.9</v>
       </c>
       <c r="E49" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$Z$2:$Z$264,Schemes!$H$2:$H$264,$A49)</f>
+        <f aca="false">SUMIFS(Schemes!$Z$2:$Z$266,Schemes!$H$2:$H$266,$A49)</f>
         <v>15.3</v>
       </c>
       <c r="F49" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$AA$2:$AA$264,Schemes!$H$2:$H$264,$A49)</f>
+        <f aca="false">SUMIFS(Schemes!$AA$2:$AA$266,Schemes!$H$2:$H$266,$A49)</f>
         <v>0.7</v>
       </c>
       <c r="G49" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$AB$2:$AB$264,Schemes!$H$2:$H$264,$A49)</f>
+        <f aca="false">SUMIFS(Schemes!$AB$2:$AB$266,Schemes!$H$2:$H$266,$A49)</f>
         <v>-0.1</v>
       </c>
       <c r="H49" s="17" t="n">
@@ -7983,7 +8031,7 @@
         <v>204</v>
       </c>
       <c r="I49" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$AC$2:$AC$264,Schemes!$H$2:$H$264,$A49)</f>
+        <f aca="false">SUMIFS(Schemes!$AC$2:$AC$266,Schemes!$H$2:$H$266,$A49)</f>
         <v>41</v>
       </c>
     </row>
@@ -7992,27 +8040,27 @@
         <v>52</v>
       </c>
       <c r="B50" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$W$2:$W$264,Schemes!$H$2:$H$264,$A50)</f>
+        <f aca="false">SUMIFS(Schemes!$W$2:$W$266,Schemes!$H$2:$H$266,$A50)</f>
         <v>0</v>
       </c>
       <c r="C50" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$X$2:$X$264,Schemes!$H$2:$H$264,$A50)</f>
+        <f aca="false">SUMIFS(Schemes!$X$2:$X$266,Schemes!$H$2:$H$266,$A50)</f>
         <v>0</v>
       </c>
       <c r="D50" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$Y$2:$Y$264,Schemes!$H$2:$H$264,$A50)</f>
+        <f aca="false">SUMIFS(Schemes!$Y$2:$Y$266,Schemes!$H$2:$H$266,$A50)</f>
         <v>10.1</v>
       </c>
       <c r="E50" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$Z$2:$Z$264,Schemes!$H$2:$H$264,$A50)</f>
+        <f aca="false">SUMIFS(Schemes!$Z$2:$Z$266,Schemes!$H$2:$H$266,$A50)</f>
         <v>61</v>
       </c>
       <c r="F50" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$AA$2:$AA$264,Schemes!$H$2:$H$264,$A50)</f>
+        <f aca="false">SUMIFS(Schemes!$AA$2:$AA$266,Schemes!$H$2:$H$266,$A50)</f>
         <v>61</v>
       </c>
       <c r="G50" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$AB$2:$AB$264,Schemes!$H$2:$H$264,$A50)</f>
+        <f aca="false">SUMIFS(Schemes!$AB$2:$AB$266,Schemes!$H$2:$H$266,$A50)</f>
         <v>152.9</v>
       </c>
       <c r="H50" s="17" t="n">
@@ -8020,7 +8068,7 @@
         <v>285</v>
       </c>
       <c r="I50" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$AC$2:$AC$264,Schemes!$H$2:$H$264,$A50)</f>
+        <f aca="false">SUMIFS(Schemes!$AC$2:$AC$266,Schemes!$H$2:$H$266,$A50)</f>
         <v>0</v>
       </c>
     </row>
@@ -8071,11 +8119,11 @@
       </c>
       <c r="D52" s="15" t="n">
         <f aca="false">SUM(D47:D51)</f>
-        <v>1912.21666666667</v>
+        <v>1926.31666666667</v>
       </c>
       <c r="E52" s="15" t="n">
         <f aca="false">SUM(E47:E51)</f>
-        <v>2146.71666666667</v>
+        <v>2156.61666666667</v>
       </c>
       <c r="F52" s="15" t="n">
         <f aca="false">SUM(F47:F51)</f>
@@ -8087,7 +8135,7 @@
       </c>
       <c r="H52" s="15" t="n">
         <f aca="false">SUM(H47:H51)</f>
-        <v>9853.55</v>
+        <v>9877.55</v>
       </c>
       <c r="I52" s="15" t="n">
         <f aca="false">SUM(I47:I51)</f>
@@ -8135,27 +8183,27 @@
         <v>41</v>
       </c>
       <c r="B57" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$W$2:$W$264,Schemes!$F$2:$F$264,$A57)</f>
+        <f aca="false">SUMIFS(Schemes!$W$2:$W$266,Schemes!$F$2:$F$266,$A57)</f>
         <v>105.6</v>
       </c>
       <c r="C57" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$X$2:$X$264,Schemes!$F$2:$F$264,$A57)</f>
+        <f aca="false">SUMIFS(Schemes!$X$2:$X$266,Schemes!$F$2:$F$266,$A57)</f>
         <v>550.3</v>
       </c>
       <c r="D57" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$Y$2:$Y$264,Schemes!$F$2:$F$264,$A57)</f>
+        <f aca="false">SUMIFS(Schemes!$Y$2:$Y$266,Schemes!$F$2:$F$266,$A57)</f>
         <v>762.3</v>
       </c>
       <c r="E57" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$Z$2:$Z$264,Schemes!$F$2:$F$264,$A57)</f>
+        <f aca="false">SUMIFS(Schemes!$Z$2:$Z$266,Schemes!$F$2:$F$266,$A57)</f>
         <v>1305.6</v>
       </c>
       <c r="F57" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$AA$2:$AA$264,Schemes!$F$2:$F$264,$A57)</f>
+        <f aca="false">SUMIFS(Schemes!$AA$2:$AA$266,Schemes!$F$2:$F$266,$A57)</f>
         <v>803.6</v>
       </c>
       <c r="G57" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$AB$2:$AB$264,Schemes!$F$2:$F$264,$A57)</f>
+        <f aca="false">SUMIFS(Schemes!$AB$2:$AB$266,Schemes!$F$2:$F$266,$A57)</f>
         <v>1573.6</v>
       </c>
       <c r="H57" s="17" t="n">
@@ -8168,27 +8216,27 @@
         <v>42</v>
       </c>
       <c r="B58" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$W$2:$W$264,Schemes!$F$2:$F$264,$A58)</f>
+        <f aca="false">SUMIFS(Schemes!$W$2:$W$266,Schemes!$F$2:$F$266,$A58)</f>
         <v>49.2</v>
       </c>
       <c r="C58" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$X$2:$X$264,Schemes!$F$2:$F$264,$A58)</f>
+        <f aca="false">SUMIFS(Schemes!$X$2:$X$266,Schemes!$F$2:$F$266,$A58)</f>
         <v>167.6</v>
       </c>
       <c r="D58" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$Y$2:$Y$264,Schemes!$F$2:$F$264,$A58)</f>
+        <f aca="false">SUMIFS(Schemes!$Y$2:$Y$266,Schemes!$F$2:$F$266,$A58)</f>
         <v>119.7</v>
       </c>
       <c r="E58" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$Z$2:$Z$264,Schemes!$F$2:$F$264,$A58)</f>
+        <f aca="false">SUMIFS(Schemes!$Z$2:$Z$266,Schemes!$F$2:$F$266,$A58)</f>
         <v>56.5</v>
       </c>
       <c r="F58" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$AA$2:$AA$264,Schemes!$F$2:$F$264,$A58)</f>
+        <f aca="false">SUMIFS(Schemes!$AA$2:$AA$266,Schemes!$F$2:$F$266,$A58)</f>
         <v>5</v>
       </c>
       <c r="G58" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$AB$2:$AB$264,Schemes!$F$2:$F$264,$A58)</f>
+        <f aca="false">SUMIFS(Schemes!$AB$2:$AB$266,Schemes!$F$2:$F$266,$A58)</f>
         <v>0</v>
       </c>
       <c r="H58" s="17" t="n">
@@ -8201,27 +8249,27 @@
         <v>43</v>
       </c>
       <c r="B59" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$W$2:$W$264,Schemes!$F$2:$F$264,$A59)</f>
+        <f aca="false">SUMIFS(Schemes!$W$2:$W$266,Schemes!$F$2:$F$266,$A59)</f>
         <v>272.6</v>
       </c>
       <c r="C59" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$X$2:$X$264,Schemes!$F$2:$F$264,$A59)</f>
+        <f aca="false">SUMIFS(Schemes!$X$2:$X$266,Schemes!$F$2:$F$266,$A59)</f>
         <v>996.1</v>
       </c>
       <c r="D59" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$Y$2:$Y$264,Schemes!$F$2:$F$264,$A59)</f>
+        <f aca="false">SUMIFS(Schemes!$Y$2:$Y$266,Schemes!$F$2:$F$266,$A59)</f>
         <v>331.1</v>
       </c>
       <c r="E59" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$Z$2:$Z$264,Schemes!$F$2:$F$264,$A59)</f>
+        <f aca="false">SUMIFS(Schemes!$Z$2:$Z$266,Schemes!$F$2:$F$266,$A59)</f>
         <v>260.1</v>
       </c>
       <c r="F59" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$AA$2:$AA$264,Schemes!$F$2:$F$264,$A59)</f>
+        <f aca="false">SUMIFS(Schemes!$AA$2:$AA$266,Schemes!$F$2:$F$266,$A59)</f>
         <v>14.5</v>
       </c>
       <c r="G59" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$AB$2:$AB$264,Schemes!$F$2:$F$264,$A59)</f>
+        <f aca="false">SUMIFS(Schemes!$AB$2:$AB$266,Schemes!$F$2:$F$266,$A59)</f>
         <v>-0.4</v>
       </c>
       <c r="H59" s="17" t="n">
@@ -8234,32 +8282,32 @@
         <v>44</v>
       </c>
       <c r="B60" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$W$2:$W$264,Schemes!$F$2:$F$264,$A60)</f>
+        <f aca="false">SUMIFS(Schemes!$W$2:$W$266,Schemes!$F$2:$F$266,$A60)</f>
         <v>161</v>
       </c>
       <c r="C60" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$X$2:$X$264,Schemes!$F$2:$F$264,$A60)</f>
+        <f aca="false">SUMIFS(Schemes!$X$2:$X$266,Schemes!$F$2:$F$266,$A60)</f>
         <v>641.5</v>
       </c>
       <c r="D60" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$Y$2:$Y$264,Schemes!$F$2:$F$264,$A60)</f>
-        <v>508.1</v>
+        <f aca="false">SUMIFS(Schemes!$Y$2:$Y$266,Schemes!$F$2:$F$266,$A60)</f>
+        <v>522.2</v>
       </c>
       <c r="E60" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$Z$2:$Z$264,Schemes!$F$2:$F$264,$A60)</f>
-        <v>333.5</v>
+        <f aca="false">SUMIFS(Schemes!$Z$2:$Z$266,Schemes!$F$2:$F$266,$A60)</f>
+        <v>343.4</v>
       </c>
       <c r="F60" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$AA$2:$AA$264,Schemes!$F$2:$F$264,$A60)</f>
+        <f aca="false">SUMIFS(Schemes!$AA$2:$AA$266,Schemes!$F$2:$F$266,$A60)</f>
         <v>27.9</v>
       </c>
       <c r="G60" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$AB$2:$AB$264,Schemes!$F$2:$F$264,$A60)</f>
+        <f aca="false">SUMIFS(Schemes!$AB$2:$AB$266,Schemes!$F$2:$F$266,$A60)</f>
         <v>0</v>
       </c>
       <c r="H60" s="17" t="n">
         <f aca="false">SUM(B60:G60)</f>
-        <v>1672</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8309,11 +8357,11 @@
       </c>
       <c r="D62" s="15" t="n">
         <f aca="false">SUM(D57:D61)</f>
-        <v>1912.21666666667</v>
+        <v>1926.31666666667</v>
       </c>
       <c r="E62" s="15" t="n">
         <f aca="false">SUM(E57:E61)</f>
-        <v>2146.71666666667</v>
+        <v>2156.61666666667</v>
       </c>
       <c r="F62" s="15" t="n">
         <f aca="false">SUM(F57:F61)</f>
@@ -8325,7 +8373,7 @@
       </c>
       <c r="H62" s="15" t="n">
         <f aca="false">SUM(H57:H61)</f>
-        <v>9853.55</v>
+        <v>9877.55</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8364,27 +8412,27 @@
         <v>68</v>
       </c>
       <c r="B66" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$W$2:$W$264,Schemes!$T$2:$T$264,$A66)</f>
+        <f aca="false">SUMIFS(Schemes!$W$2:$W$266,Schemes!$T$2:$T$266,$A66)</f>
         <v>588.4</v>
       </c>
       <c r="C66" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$X$2:$X$264,Schemes!$T$2:$T$264,$A66)</f>
+        <f aca="false">SUMIFS(Schemes!$X$2:$X$266,Schemes!$T$2:$T$266,$A66)</f>
         <v>2353</v>
       </c>
       <c r="D66" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$Y$2:$Y$264,Schemes!$T$2:$T$264,$A66)</f>
+        <f aca="false">SUMIFS(Schemes!$Y$2:$Y$266,Schemes!$T$2:$T$266,$A66)</f>
         <v>552.6</v>
       </c>
       <c r="E66" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$Z$2:$Z$264,Schemes!$T$2:$T$264,$A66)</f>
+        <f aca="false">SUMIFS(Schemes!$Z$2:$Z$266,Schemes!$T$2:$T$266,$A66)</f>
         <v>243.3</v>
       </c>
       <c r="F66" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$AA$2:$AA$264,Schemes!$T$2:$T$264,$A66)</f>
+        <f aca="false">SUMIFS(Schemes!$AA$2:$AA$266,Schemes!$T$2:$T$266,$A66)</f>
         <v>221.9</v>
       </c>
       <c r="G66" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$AB$2:$AB$264,Schemes!$T$2:$T$264,$A66)</f>
+        <f aca="false">SUMIFS(Schemes!$AB$2:$AB$266,Schemes!$T$2:$T$266,$A66)</f>
         <v>104.8</v>
       </c>
       <c r="H66" s="17" t="n">
@@ -8397,27 +8445,27 @@
         <v>69</v>
       </c>
       <c r="B67" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$W$2:$W$264,Schemes!$T$2:$T$264,$A67)</f>
+        <f aca="false">SUMIFS(Schemes!$W$2:$W$266,Schemes!$T$2:$T$266,$A67)</f>
         <v>0</v>
       </c>
       <c r="C67" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$X$2:$X$264,Schemes!$T$2:$T$264,$A67)</f>
+        <f aca="false">SUMIFS(Schemes!$X$2:$X$266,Schemes!$T$2:$T$266,$A67)</f>
         <v>2.5</v>
       </c>
       <c r="D67" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$Y$2:$Y$264,Schemes!$T$2:$T$264,$A67)</f>
+        <f aca="false">SUMIFS(Schemes!$Y$2:$Y$266,Schemes!$T$2:$T$266,$A67)</f>
         <v>553.3</v>
       </c>
       <c r="E67" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$Z$2:$Z$264,Schemes!$T$2:$T$264,$A67)</f>
+        <f aca="false">SUMIFS(Schemes!$Z$2:$Z$266,Schemes!$T$2:$T$266,$A67)</f>
         <v>1046.3</v>
       </c>
       <c r="F67" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$AA$2:$AA$264,Schemes!$T$2:$T$264,$A67)</f>
+        <f aca="false">SUMIFS(Schemes!$AA$2:$AA$266,Schemes!$T$2:$T$266,$A67)</f>
         <v>493.3</v>
       </c>
       <c r="G67" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$AB$2:$AB$264,Schemes!$T$2:$T$264,$A67)</f>
+        <f aca="false">SUMIFS(Schemes!$AB$2:$AB$266,Schemes!$T$2:$T$266,$A67)</f>
         <v>1468.6</v>
       </c>
       <c r="H67" s="17" t="n">
@@ -8430,32 +8478,32 @@
         <v>70</v>
       </c>
       <c r="B68" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$W$2:$W$264,Schemes!$T$2:$T$264,$A68)</f>
+        <f aca="false">SUMIFS(Schemes!$W$2:$W$266,Schemes!$T$2:$T$266,$A68)</f>
         <v>0</v>
       </c>
       <c r="C68" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$X$2:$X$264,Schemes!$T$2:$T$264,$A68)</f>
+        <f aca="false">SUMIFS(Schemes!$X$2:$X$266,Schemes!$T$2:$T$266,$A68)</f>
         <v>0</v>
       </c>
       <c r="D68" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$Y$2:$Y$264,Schemes!$T$2:$T$264,$A68)</f>
-        <v>615.3</v>
+        <f aca="false">SUMIFS(Schemes!$Y$2:$Y$266,Schemes!$T$2:$T$266,$A68)</f>
+        <v>629.4</v>
       </c>
       <c r="E68" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$Z$2:$Z$264,Schemes!$T$2:$T$264,$A68)</f>
-        <v>666.1</v>
+        <f aca="false">SUMIFS(Schemes!$Z$2:$Z$266,Schemes!$T$2:$T$266,$A68)</f>
+        <v>676</v>
       </c>
       <c r="F68" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$AA$2:$AA$264,Schemes!$T$2:$T$264,$A68)</f>
+        <f aca="false">SUMIFS(Schemes!$AA$2:$AA$266,Schemes!$T$2:$T$266,$A68)</f>
         <v>135.8</v>
       </c>
       <c r="G68" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$AB$2:$AB$264,Schemes!$T$2:$T$264,$A68)</f>
+        <f aca="false">SUMIFS(Schemes!$AB$2:$AB$266,Schemes!$T$2:$T$266,$A68)</f>
         <v>-0.2</v>
       </c>
       <c r="H68" s="17" t="n">
         <f aca="false">SUM(B68:G68)</f>
-        <v>1417</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8505,11 +8553,11 @@
       </c>
       <c r="D70" s="15" t="n">
         <f aca="false">SUM(D66:D69)</f>
-        <v>1912.21666666667</v>
+        <v>1926.31666666667</v>
       </c>
       <c r="E70" s="15" t="n">
         <f aca="false">SUM(E66:E69)</f>
-        <v>2146.71666666667</v>
+        <v>2156.61666666667</v>
       </c>
       <c r="F70" s="15" t="n">
         <f aca="false">SUM(F66:F69)</f>
@@ -8521,7 +8569,7 @@
       </c>
       <c r="H70" s="15" t="n">
         <f aca="false">SUM(H66:H69)</f>
-        <v>9853.55</v>
+        <v>9877.55</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8728,7 +8776,7 @@
         <v>203</v>
       </c>
       <c r="E5" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$D$2:$D$264,$A5,Schemes!$F$2:$F$264,"Audit land – within site",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$D$2:$D$266,$A5,Schemes!$F$2:$F$266,"Audit land – within site",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>371</v>
       </c>
       <c r="F5" s="12" t="n">
@@ -8736,11 +8784,11 @@
         <v>148</v>
       </c>
       <c r="G5" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$D$2:$D$264,$A5,Schemes!$F$2:$F$264,"Audit land – edge (check)",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$D$2:$D$266,$A5,Schemes!$F$2:$F$266,"Audit land – edge (check)",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>0</v>
       </c>
       <c r="H5" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$D$2:$D$264,$A5,Schemes!$F$2:$F$264,"City – outside audit land",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$D$2:$D$266,$A5,Schemes!$F$2:$F$266,"City – outside audit land",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>44</v>
       </c>
       <c r="I5" s="17" t="n">
@@ -8765,7 +8813,7 @@
         <v>1933</v>
       </c>
       <c r="E6" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$D$2:$D$264,$A6,Schemes!$F$2:$F$264,"Audit land – within site",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$D$2:$D$266,$A6,Schemes!$F$2:$F$266,"Audit land – within site",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>1037</v>
       </c>
       <c r="F6" s="12" t="n">
@@ -8773,11 +8821,11 @@
         <v>938</v>
       </c>
       <c r="G6" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$D$2:$D$264,$A6,Schemes!$F$2:$F$264,"Audit land – edge (check)",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$D$2:$D$266,$A6,Schemes!$F$2:$F$266,"Audit land – edge (check)",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>38</v>
       </c>
       <c r="H6" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$D$2:$D$264,$A6,Schemes!$F$2:$F$264,"City – outside audit land",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$D$2:$D$266,$A6,Schemes!$F$2:$F$266,"City – outside audit land",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>223</v>
       </c>
       <c r="I6" s="17" t="n">
@@ -8802,7 +8850,7 @@
         <v>2355</v>
       </c>
       <c r="E7" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$D$2:$D$264,$A7,Schemes!$F$2:$F$264,"Audit land – within site",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$D$2:$D$266,$A7,Schemes!$F$2:$F$266,"Audit land – within site",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>1634</v>
       </c>
       <c r="F7" s="12" t="n">
@@ -8810,11 +8858,11 @@
         <v>1197</v>
       </c>
       <c r="G7" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$D$2:$D$264,$A7,Schemes!$F$2:$F$264,"Audit land – edge (check)",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$D$2:$D$266,$A7,Schemes!$F$2:$F$266,"Audit land – edge (check)",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>43</v>
       </c>
       <c r="H7" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$D$2:$D$264,$A7,Schemes!$F$2:$F$264,"City – outside audit land",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$D$2:$D$266,$A7,Schemes!$F$2:$F$266,"City – outside audit land",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>1133</v>
       </c>
       <c r="I7" s="17" t="n">
@@ -8839,7 +8887,7 @@
         <v>3633</v>
       </c>
       <c r="E8" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$D$2:$D$264,$A8,Schemes!$F$2:$F$264,"Audit land – within site",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$D$2:$D$266,$A8,Schemes!$F$2:$F$266,"Audit land – within site",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>332</v>
       </c>
       <c r="F8" s="12" t="n">
@@ -8847,11 +8895,11 @@
         <v>3301</v>
       </c>
       <c r="G8" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$D$2:$D$264,$A8,Schemes!$F$2:$F$264,"Audit land – edge (check)",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$D$2:$D$266,$A8,Schemes!$F$2:$F$266,"Audit land – edge (check)",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>215</v>
       </c>
       <c r="H8" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$D$2:$D$264,$A8,Schemes!$F$2:$F$264,"City – outside audit land",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$D$2:$D$266,$A8,Schemes!$F$2:$F$266,"City – outside audit land",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>378</v>
       </c>
       <c r="I8" s="17" t="n">
@@ -8876,7 +8924,7 @@
         <v>646</v>
       </c>
       <c r="E9" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$D$2:$D$264,$A9,Schemes!$F$2:$F$264,"Audit land – within site",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$D$2:$D$266,$A9,Schemes!$F$2:$F$266,"Audit land – within site",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>66</v>
       </c>
       <c r="F9" s="12" t="n">
@@ -8884,11 +8932,11 @@
         <v>584</v>
       </c>
       <c r="G9" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$D$2:$D$264,$A9,Schemes!$F$2:$F$264,"Audit land – edge (check)",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$D$2:$D$266,$A9,Schemes!$F$2:$F$266,"Audit land – edge (check)",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>0</v>
       </c>
       <c r="H9" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$D$2:$D$264,$A9,Schemes!$F$2:$F$264,"City – outside audit land",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$D$2:$D$266,$A9,Schemes!$F$2:$F$266,"City – outside audit land",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>24</v>
       </c>
       <c r="I9" s="17" t="n">
@@ -8913,7 +8961,7 @@
         <v>3699</v>
       </c>
       <c r="E10" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$D$2:$D$264,$A10,Schemes!$F$2:$F$264,"Audit land – within site",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$D$2:$D$266,$A10,Schemes!$F$2:$F$266,"Audit land – within site",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>1124</v>
       </c>
       <c r="F10" s="12" t="n">
@@ -8921,11 +8969,11 @@
         <v>2575</v>
       </c>
       <c r="G10" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$D$2:$D$264,$A10,Schemes!$F$2:$F$264,"Audit land – edge (check)",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$D$2:$D$266,$A10,Schemes!$F$2:$F$266,"Audit land – edge (check)",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>165</v>
       </c>
       <c r="H10" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$D$2:$D$264,$A10,Schemes!$F$2:$F$264,"City – outside audit land",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$D$2:$D$266,$A10,Schemes!$F$2:$F$266,"City – outside audit land",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>631</v>
       </c>
       <c r="I10" s="17" t="n">
@@ -8950,7 +8998,7 @@
         <v>25</v>
       </c>
       <c r="E11" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$D$2:$D$264,$A11,Schemes!$F$2:$F$264,"Audit land – within site",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$D$2:$D$266,$A11,Schemes!$F$2:$F$266,"Audit land – within site",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>0</v>
       </c>
       <c r="F11" s="12" t="n">
@@ -8958,11 +9006,11 @@
         <v>25</v>
       </c>
       <c r="G11" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$D$2:$D$264,$A11,Schemes!$F$2:$F$264,"Audit land – edge (check)",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$D$2:$D$266,$A11,Schemes!$F$2:$F$266,"Audit land – edge (check)",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>0</v>
       </c>
       <c r="H11" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$D$2:$D$264,$A11,Schemes!$F$2:$F$264,"City – outside audit land",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$D$2:$D$266,$A11,Schemes!$F$2:$F$266,"City – outside audit land",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>50</v>
       </c>
       <c r="I11" s="17" t="n">
@@ -8987,7 +9035,7 @@
         <v>615</v>
       </c>
       <c r="E12" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$D$2:$D$264,$A12,Schemes!$F$2:$F$264,"Audit land – within site",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$D$2:$D$266,$A12,Schemes!$F$2:$F$266,"Audit land – within site",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>231</v>
       </c>
       <c r="F12" s="12" t="n">
@@ -8995,11 +9043,11 @@
         <v>469</v>
       </c>
       <c r="G12" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$D$2:$D$264,$A12,Schemes!$F$2:$F$264,"Audit land – edge (check)",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$D$2:$D$266,$A12,Schemes!$F$2:$F$266,"Audit land – edge (check)",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>0</v>
       </c>
       <c r="H12" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$D$2:$D$264,$A12,Schemes!$F$2:$F$264,"City – outside audit land",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$D$2:$D$266,$A12,Schemes!$F$2:$F$266,"City – outside audit land",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>69</v>
       </c>
       <c r="I12" s="17" t="n">
@@ -9024,7 +9072,7 @@
         <v>956</v>
       </c>
       <c r="E13" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$D$2:$D$264,$A13,Schemes!$F$2:$F$264,"Audit land – within site",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$D$2:$D$266,$A13,Schemes!$F$2:$F$266,"Audit land – within site",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>413</v>
       </c>
       <c r="F13" s="12" t="n">
@@ -9032,11 +9080,11 @@
         <v>683</v>
       </c>
       <c r="G13" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$D$2:$D$264,$A13,Schemes!$F$2:$F$264,"Audit land – edge (check)",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$D$2:$D$266,$A13,Schemes!$F$2:$F$266,"Audit land – edge (check)",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>17</v>
       </c>
       <c r="H13" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$D$2:$D$264,$A13,Schemes!$F$2:$F$264,"City – outside audit land",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$D$2:$D$266,$A13,Schemes!$F$2:$F$266,"City – outside audit land",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>293</v>
       </c>
       <c r="I13" s="17" t="n">
@@ -9116,24 +9164,24 @@
         <v>100</v>
       </c>
       <c r="B19" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$I$2:$I$264,$A19,Schemes!$F$2:$F$264,"Audit land – within site",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$I$2:$I$266,$A19,Schemes!$F$2:$F$266,"Audit land – within site",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>3763</v>
       </c>
       <c r="C19" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$I$2:$I$264,$A19,Schemes!$F$2:$F$264,"Audit land – edge (check)",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$I$2:$I$266,$A19,Schemes!$F$2:$F$266,"Audit land – edge (check)",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>368</v>
       </c>
       <c r="D19" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$I$2:$I$264,$A19,Schemes!$F$2:$F$264,"City – outside audit land",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$I$2:$I$266,$A19,Schemes!$F$2:$F$266,"City – outside audit land",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>2499</v>
       </c>
       <c r="E19" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$I$2:$I$264,$A19,Schemes!$F$2:$F$264,"County – audit not yet supplied",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
-        <v>1549</v>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$I$2:$I$266,$A19,Schemes!$F$2:$F$266,"County – audit not yet supplied",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
+        <v>1573</v>
       </c>
       <c r="F19" s="17" t="n">
         <f aca="false">SUM(B19:E19)</f>
-        <v>8179</v>
+        <v>8203</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9141,19 +9189,19 @@
         <v>101</v>
       </c>
       <c r="B20" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$I$2:$I$264,$A20,Schemes!$F$2:$F$264,"Audit land – within site",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$I$2:$I$266,$A20,Schemes!$F$2:$F$266,"Audit land – within site",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>442</v>
       </c>
       <c r="C20" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$I$2:$I$264,$A20,Schemes!$F$2:$F$264,"Audit land – edge (check)",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$I$2:$I$266,$A20,Schemes!$F$2:$F$266,"Audit land – edge (check)",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>85</v>
       </c>
       <c r="D20" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$I$2:$I$264,$A20,Schemes!$F$2:$F$264,"City – outside audit land",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$I$2:$I$266,$A20,Schemes!$F$2:$F$266,"City – outside audit land",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>346</v>
       </c>
       <c r="E20" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$I$2:$I$264,$A20,Schemes!$F$2:$F$264,"County – audit not yet supplied",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$I$2:$I$266,$A20,Schemes!$F$2:$F$266,"County – audit not yet supplied",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>365</v>
       </c>
       <c r="F20" s="17" t="n">
@@ -9166,19 +9214,19 @@
         <v>102</v>
       </c>
       <c r="B21" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$I$2:$I$264,$A21,Schemes!$F$2:$F$264,"Audit land – within site",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$I$2:$I$266,$A21,Schemes!$F$2:$F$266,"Audit land – within site",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>285</v>
       </c>
       <c r="C21" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$I$2:$I$264,$A21,Schemes!$F$2:$F$264,"Audit land – edge (check)",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$I$2:$I$266,$A21,Schemes!$F$2:$F$266,"Audit land – edge (check)",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>0</v>
       </c>
       <c r="D21" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$I$2:$I$264,$A21,Schemes!$F$2:$F$264,"City – outside audit land",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$I$2:$I$266,$A21,Schemes!$F$2:$F$266,"City – outside audit land",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>0</v>
       </c>
       <c r="E21" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$I$2:$I$264,$A21,Schemes!$F$2:$F$264,"County – audit not yet supplied",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$I$2:$I$266,$A21,Schemes!$F$2:$F$266,"County – audit not yet supplied",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>31</v>
       </c>
       <c r="F21" s="17" t="n">
@@ -9191,19 +9239,19 @@
         <v>103</v>
       </c>
       <c r="B22" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$I$2:$I$264,$A22,Schemes!$F$2:$F$264,"Audit land – within site",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$I$2:$I$266,$A22,Schemes!$F$2:$F$266,"Audit land – within site",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>718</v>
       </c>
       <c r="C22" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$I$2:$I$264,$A22,Schemes!$F$2:$F$264,"Audit land – edge (check)",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$I$2:$I$266,$A22,Schemes!$F$2:$F$266,"Audit land – edge (check)",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>25</v>
       </c>
       <c r="D22" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$I$2:$I$264,$A22,Schemes!$F$2:$F$264,"City – outside audit land",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$I$2:$I$266,$A22,Schemes!$F$2:$F$266,"City – outside audit land",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>0</v>
       </c>
       <c r="E22" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$I$2:$I$264,$A22,Schemes!$F$2:$F$264,"County – audit not yet supplied",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$I$2:$I$266,$A22,Schemes!$F$2:$F$266,"County – audit not yet supplied",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>0</v>
       </c>
       <c r="F22" s="17" t="n">
@@ -9229,11 +9277,11 @@
       </c>
       <c r="E23" s="15" t="n">
         <f aca="false">SUM(E19:E22)</f>
-        <v>1945</v>
+        <v>1969</v>
       </c>
       <c r="F23" s="15" t="n">
         <f aca="false">SUM(F19:F22)</f>
-        <v>10476</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9269,27 +9317,27 @@
         <v>29</v>
       </c>
       <c r="B27" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A27,Schemes!$K$2:$K$264,"Complete")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A27,Schemes!$K$2:$K$266,"Complete")</f>
         <v>974</v>
       </c>
       <c r="C27" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A27,Schemes!$K$2:$K$264,"Under construction")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A27,Schemes!$K$2:$K$266,"Under construction")</f>
         <v>3347</v>
       </c>
       <c r="D27" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A27,Schemes!$K$2:$K$264,"Not started – permission live")</f>
-        <v>4445</v>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A27,Schemes!$K$2:$K$266,"Not started – permission live")</f>
+        <v>4469</v>
       </c>
       <c r="E27" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A27,Schemes!$K$2:$K$264,"Stalled (CIS)")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A27,Schemes!$K$2:$K$266,"Stalled (CIS)")</f>
         <v>156</v>
       </c>
       <c r="F27" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A27,Schemes!$K$2:$K$264,"Not started – past expiry")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A27,Schemes!$K$2:$K$266,"Not started – past expiry")</f>
         <v>278</v>
       </c>
       <c r="G27" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A27,Schemes!$K$2:$K$264,"In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A27,Schemes!$K$2:$K$266,"In planning")</f>
         <v>82</v>
       </c>
     </row>
@@ -9298,27 +9346,27 @@
         <v>50</v>
       </c>
       <c r="B28" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A28,Schemes!$K$2:$K$264,"Complete")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A28,Schemes!$K$2:$K$266,"Complete")</f>
         <v>207</v>
       </c>
       <c r="C28" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A28,Schemes!$K$2:$K$264,"Under construction")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A28,Schemes!$K$2:$K$266,"Under construction")</f>
         <v>546</v>
       </c>
       <c r="D28" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A28,Schemes!$K$2:$K$264,"Not started – permission live")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A28,Schemes!$K$2:$K$266,"Not started – permission live")</f>
         <v>218</v>
       </c>
       <c r="E28" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A28,Schemes!$K$2:$K$264,"Stalled (CIS)")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A28,Schemes!$K$2:$K$266,"Stalled (CIS)")</f>
         <v>0</v>
       </c>
       <c r="F28" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A28,Schemes!$K$2:$K$264,"Not started – past expiry")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A28,Schemes!$K$2:$K$266,"Not started – past expiry")</f>
         <v>0</v>
       </c>
       <c r="G28" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A28,Schemes!$K$2:$K$264,"In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A28,Schemes!$K$2:$K$266,"In planning")</f>
         <v>173</v>
       </c>
     </row>
@@ -9327,27 +9375,27 @@
         <v>51</v>
       </c>
       <c r="B29" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A29,Schemes!$K$2:$K$264,"Complete")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A29,Schemes!$K$2:$K$266,"Complete")</f>
         <v>94</v>
       </c>
       <c r="C29" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A29,Schemes!$K$2:$K$264,"Under construction")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A29,Schemes!$K$2:$K$266,"Under construction")</f>
         <v>171</v>
       </c>
       <c r="D29" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A29,Schemes!$K$2:$K$264,"Not started – permission live")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A29,Schemes!$K$2:$K$266,"Not started – permission live")</f>
         <v>33</v>
       </c>
       <c r="E29" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A29,Schemes!$K$2:$K$264,"Stalled (CIS)")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A29,Schemes!$K$2:$K$266,"Stalled (CIS)")</f>
         <v>0</v>
       </c>
       <c r="F29" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A29,Schemes!$K$2:$K$264,"Not started – past expiry")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A29,Schemes!$K$2:$K$266,"Not started – past expiry")</f>
         <v>33</v>
       </c>
       <c r="G29" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A29,Schemes!$K$2:$K$264,"In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A29,Schemes!$K$2:$K$266,"In planning")</f>
         <v>8</v>
       </c>
     </row>
@@ -9356,27 +9404,27 @@
         <v>52</v>
       </c>
       <c r="B30" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A30,Schemes!$K$2:$K$264,"Complete")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A30,Schemes!$K$2:$K$266,"Complete")</f>
         <v>0</v>
       </c>
       <c r="C30" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A30,Schemes!$K$2:$K$264,"Under construction")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A30,Schemes!$K$2:$K$266,"Under construction")</f>
         <v>0</v>
       </c>
       <c r="D30" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A30,Schemes!$K$2:$K$264,"Not started – permission live")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A30,Schemes!$K$2:$K$266,"Not started – permission live")</f>
         <v>285</v>
       </c>
       <c r="E30" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A30,Schemes!$K$2:$K$264,"Stalled (CIS)")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A30,Schemes!$K$2:$K$266,"Stalled (CIS)")</f>
         <v>0</v>
       </c>
       <c r="F30" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A30,Schemes!$K$2:$K$264,"Not started – past expiry")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A30,Schemes!$K$2:$K$266,"Not started – past expiry")</f>
         <v>0</v>
       </c>
       <c r="G30" s="12" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$H$2:$H$264,$A30,Schemes!$K$2:$K$264,"In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$H$2:$H$266,$A30,Schemes!$K$2:$K$266,"In planning")</f>
         <v>0</v>
       </c>
     </row>
@@ -9394,7 +9442,7 @@
       </c>
       <c r="D31" s="15" t="n">
         <f aca="false">SUM(D27:D30)</f>
-        <v>4981</v>
+        <v>5005</v>
       </c>
       <c r="E31" s="15" t="n">
         <f aca="false">SUM(E27:E30)</f>
@@ -9639,11 +9687,11 @@
         <v>138</v>
       </c>
       <c r="E42" s="15" t="n">
-        <f aca="false">SUMIFS(Schemes!$M$2:$M$264,Schemes!$I$2:$I$264,"Student (PBSA)",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$M$2:$M$266,Schemes!$I$2:$I$266,"Student (PBSA)",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>743</v>
       </c>
       <c r="F42" s="15" t="n">
-        <f aca="false">SUMIFS(Schemes!$N$2:$N$264,Schemes!$I$2:$I$264,"Student (PBSA)",Schemes!$K$2:$K$264,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$264,"&lt;&gt;In planning")</f>
+        <f aca="false">SUMIFS(Schemes!$N$2:$N$266,Schemes!$I$2:$I$266,"Student (PBSA)",Schemes!$K$2:$K$266,"&lt;&gt;Not started – past expiry",Schemes!$K$2:$K$266,"&lt;&gt;In planning")</f>
         <v>2142</v>
       </c>
     </row>
@@ -18171,7 +18219,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AC264"/>
+  <dimension ref="A1:AC266"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -35053,7 +35101,7 @@
         <v>1295</v>
       </c>
       <c r="E204" s="23" t="s">
-        <v>356</v>
+        <v>1482</v>
       </c>
       <c r="F204" s="23" t="s">
         <v>44</v>
@@ -35069,34 +35117,36 @@
         <v>331</v>
       </c>
       <c r="K204" s="23" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="L204" s="23" t="s">
-        <v>23</v>
+        <v>177</v>
       </c>
       <c r="M204" s="23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N204" s="23"/>
       <c r="O204" s="23" t="s">
-        <v>1482</v>
-      </c>
-      <c r="P204" s="23" t="s">
         <v>1483</v>
       </c>
+      <c r="P204" s="23"/>
       <c r="Q204" s="23" t="s">
         <v>1484</v>
       </c>
-      <c r="R204" s="23"/>
-      <c r="S204" s="23"/>
+      <c r="R204" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="S204" s="23" t="s">
+        <v>117</v>
+      </c>
       <c r="T204" s="23" t="s">
-        <v>344</v>
+        <v>70</v>
       </c>
       <c r="U204" s="23" t="s">
-        <v>345</v>
+        <v>1485</v>
       </c>
       <c r="V204" s="23" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W204" s="23" t="n">
         <v>0</v>
@@ -35105,10 +35155,10 @@
         <v>0</v>
       </c>
       <c r="Y204" s="23" t="n">
-        <v>0</v>
+        <v>8.2</v>
       </c>
       <c r="Z204" s="23" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA204" s="23" t="n">
         <v>0</v>
@@ -35122,19 +35172,19 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="23" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="B205" s="23" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="C205" s="23" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="D205" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E205" s="23" t="s">
-        <v>1302</v>
+        <v>356</v>
       </c>
       <c r="F205" s="23" t="s">
         <v>44</v>
@@ -35150,44 +35200,40 @@
         <v>331</v>
       </c>
       <c r="K205" s="23" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="L205" s="23" t="s">
-        <v>391</v>
+        <v>23</v>
       </c>
       <c r="M205" s="23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N205" s="23"/>
       <c r="O205" s="23" t="s">
-        <v>1240</v>
+        <v>1489</v>
       </c>
       <c r="P205" s="23" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="Q205" s="23" t="s">
-        <v>972</v>
-      </c>
-      <c r="R205" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="S205" s="23" t="s">
-        <v>131</v>
-      </c>
+        <v>1491</v>
+      </c>
+      <c r="R205" s="23"/>
+      <c r="S205" s="23"/>
       <c r="T205" s="23" t="s">
-        <v>68</v>
+        <v>344</v>
       </c>
       <c r="U205" s="23" t="s">
-        <v>746</v>
+        <v>345</v>
       </c>
       <c r="V205" s="23" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W205" s="23" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X205" s="23" t="n">
-        <v>9.2</v>
+        <v>0</v>
       </c>
       <c r="Y205" s="23" t="n">
         <v>0</v>
@@ -35207,19 +35253,19 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="23" t="s">
-        <v>1489</v>
+        <v>1492</v>
       </c>
       <c r="B206" s="23" t="s">
-        <v>1490</v>
+        <v>1493</v>
       </c>
       <c r="C206" s="23" t="s">
-        <v>1491</v>
+        <v>1494</v>
       </c>
       <c r="D206" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E206" s="23" t="s">
-        <v>1452</v>
+        <v>1302</v>
       </c>
       <c r="F206" s="23" t="s">
         <v>44</v>
@@ -35241,20 +35287,20 @@
         <v>391</v>
       </c>
       <c r="M206" s="23" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N206" s="23"/>
       <c r="O206" s="23" t="s">
-        <v>1492</v>
+        <v>1240</v>
       </c>
       <c r="P206" s="23" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="Q206" s="23" t="s">
-        <v>1494</v>
+        <v>972</v>
       </c>
       <c r="R206" s="23" t="s">
-        <v>336</v>
+        <v>124</v>
       </c>
       <c r="S206" s="23" t="s">
         <v>131</v>
@@ -35263,16 +35309,16 @@
         <v>68</v>
       </c>
       <c r="U206" s="23" t="s">
-        <v>1495</v>
+        <v>746</v>
       </c>
       <c r="V206" s="23" t="n">
         <v>0</v>
       </c>
       <c r="W206" s="23" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="X206" s="23" t="n">
-        <v>7.7</v>
+        <v>9.2</v>
       </c>
       <c r="Y206" s="23" t="n">
         <v>0</v>
@@ -35304,7 +35350,7 @@
         <v>1295</v>
       </c>
       <c r="E207" s="23" t="s">
-        <v>1296</v>
+        <v>1452</v>
       </c>
       <c r="F207" s="23" t="s">
         <v>44</v>
@@ -35339,28 +35385,28 @@
         <v>1501</v>
       </c>
       <c r="R207" s="23" t="s">
-        <v>409</v>
+        <v>336</v>
       </c>
       <c r="S207" s="23" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="T207" s="23" t="s">
         <v>68</v>
       </c>
       <c r="U207" s="23" t="s">
-        <v>718</v>
+        <v>1502</v>
       </c>
       <c r="V207" s="23" t="n">
         <v>0</v>
       </c>
       <c r="W207" s="23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X207" s="23" t="n">
-        <v>6.9</v>
+        <v>7.7</v>
       </c>
       <c r="Y207" s="23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Z207" s="23" t="n">
         <v>0</v>
@@ -35377,19 +35423,19 @@
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="23" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="B208" s="23" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="C208" s="23" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="D208" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E208" s="23" t="s">
-        <v>1302</v>
+        <v>1296</v>
       </c>
       <c r="F208" s="23" t="s">
         <v>44</v>
@@ -35405,33 +35451,35 @@
         <v>331</v>
       </c>
       <c r="K208" s="23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L208" s="23" t="s">
-        <v>477</v>
+        <v>391</v>
       </c>
       <c r="M208" s="23" t="n">
         <v>10</v>
       </c>
       <c r="N208" s="23"/>
       <c r="O208" s="23" t="s">
-        <v>1505</v>
-      </c>
-      <c r="P208" s="23"/>
+        <v>1506</v>
+      </c>
+      <c r="P208" s="23" t="s">
+        <v>1507</v>
+      </c>
       <c r="Q208" s="23" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="R208" s="23" t="s">
-        <v>116</v>
+        <v>409</v>
       </c>
       <c r="S208" s="23" t="s">
-        <v>365</v>
+        <v>120</v>
       </c>
       <c r="T208" s="23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U208" s="23" t="s">
-        <v>610</v>
+        <v>718</v>
       </c>
       <c r="V208" s="23" t="n">
         <v>0</v>
@@ -35440,13 +35488,13 @@
         <v>0</v>
       </c>
       <c r="X208" s="23" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="Y208" s="23" t="n">
-        <v>8.4</v>
+        <v>3.1</v>
       </c>
       <c r="Z208" s="23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA208" s="23" t="n">
         <v>0</v>
@@ -35460,19 +35508,19 @@
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="23" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="B209" s="23" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="C209" s="23" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="D209" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E209" s="23" t="s">
-        <v>1510</v>
+        <v>1302</v>
       </c>
       <c r="F209" s="23" t="s">
         <v>44</v>
@@ -35488,34 +35536,36 @@
         <v>331</v>
       </c>
       <c r="K209" s="23" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="L209" s="23" t="s">
-        <v>23</v>
+        <v>477</v>
       </c>
       <c r="M209" s="23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N209" s="23"/>
       <c r="O209" s="23" t="s">
-        <v>1511</v>
-      </c>
-      <c r="P209" s="23" t="s">
-        <v>780</v>
-      </c>
+        <v>1512</v>
+      </c>
+      <c r="P209" s="23"/>
       <c r="Q209" s="23" t="s">
-        <v>1512</v>
-      </c>
-      <c r="R209" s="23"/>
-      <c r="S209" s="23"/>
+        <v>1513</v>
+      </c>
+      <c r="R209" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="S209" s="23" t="s">
+        <v>365</v>
+      </c>
       <c r="T209" s="23" t="s">
-        <v>344</v>
+        <v>69</v>
       </c>
       <c r="U209" s="23" t="s">
-        <v>345</v>
+        <v>610</v>
       </c>
       <c r="V209" s="23" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W209" s="23" t="n">
         <v>0</v>
@@ -35524,10 +35574,10 @@
         <v>0</v>
       </c>
       <c r="Y209" s="23" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="Z209" s="23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA209" s="23" t="n">
         <v>0</v>
@@ -35541,19 +35591,19 @@
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="23" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B210" s="23" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="C210" s="23" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="D210" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E210" s="23" t="s">
-        <v>1329</v>
+        <v>1482</v>
       </c>
       <c r="F210" s="23" t="s">
         <v>44</v>
@@ -35569,50 +35619,48 @@
         <v>331</v>
       </c>
       <c r="K210" s="23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L210" s="23" t="s">
-        <v>391</v>
+        <v>177</v>
       </c>
       <c r="M210" s="23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N210" s="23"/>
       <c r="O210" s="23" t="s">
-        <v>1516</v>
-      </c>
-      <c r="P210" s="23" t="s">
         <v>1517</v>
       </c>
+      <c r="P210" s="23"/>
       <c r="Q210" s="23" t="s">
         <v>1518</v>
       </c>
       <c r="R210" s="23" t="s">
-        <v>791</v>
+        <v>127</v>
       </c>
       <c r="S210" s="23" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="T210" s="23" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="U210" s="23" t="s">
-        <v>1519</v>
+        <v>1231</v>
       </c>
       <c r="V210" s="23" t="n">
         <v>0</v>
       </c>
       <c r="W210" s="23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="X210" s="23" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="Y210" s="23" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="Z210" s="23" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA210" s="23" t="n">
         <v>0</v>
@@ -35626,19 +35674,19 @@
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="23" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B211" s="23" t="s">
         <v>1520</v>
       </c>
-      <c r="B211" s="23" t="s">
+      <c r="C211" s="23" t="s">
         <v>1521</v>
-      </c>
-      <c r="C211" s="23" t="s">
-        <v>1522</v>
       </c>
       <c r="D211" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E211" s="23" t="s">
-        <v>1329</v>
+        <v>1522</v>
       </c>
       <c r="F211" s="23" t="s">
         <v>44</v>
@@ -35667,10 +35715,10 @@
         <v>1523</v>
       </c>
       <c r="P211" s="23" t="s">
+        <v>780</v>
+      </c>
+      <c r="Q211" s="23" t="s">
         <v>1524</v>
-      </c>
-      <c r="Q211" s="23" t="s">
-        <v>1525</v>
       </c>
       <c r="R211" s="23"/>
       <c r="S211" s="23"/>
@@ -35707,19 +35755,19 @@
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="23" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B212" s="23" t="s">
         <v>1526</v>
       </c>
-      <c r="B212" s="23" t="s">
+      <c r="C212" s="23" t="s">
         <v>1527</v>
-      </c>
-      <c r="C212" s="23" t="s">
-        <v>1528</v>
       </c>
       <c r="D212" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E212" s="23" t="s">
-        <v>1310</v>
+        <v>1329</v>
       </c>
       <c r="F212" s="23" t="s">
         <v>44</v>
@@ -35735,48 +35783,50 @@
         <v>331</v>
       </c>
       <c r="K212" s="23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L212" s="23" t="s">
-        <v>177</v>
+        <v>391</v>
       </c>
       <c r="M212" s="23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N212" s="23"/>
       <c r="O212" s="23" t="s">
-        <v>1431</v>
-      </c>
-      <c r="P212" s="23"/>
+        <v>1528</v>
+      </c>
+      <c r="P212" s="23" t="s">
+        <v>1529</v>
+      </c>
       <c r="Q212" s="23" t="s">
-        <v>1432</v>
+        <v>1530</v>
       </c>
       <c r="R212" s="23" t="s">
+        <v>791</v>
+      </c>
+      <c r="S212" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="S212" s="23" t="s">
-        <v>596</v>
-      </c>
       <c r="T212" s="23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U212" s="23" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="V212" s="23" t="n">
         <v>0</v>
       </c>
       <c r="W212" s="23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X212" s="23" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="Y212" s="23" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Z212" s="23" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA212" s="23" t="n">
         <v>0</v>
@@ -35790,19 +35840,19 @@
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="23" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="B213" s="23" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="C213" s="23" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="D213" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E213" s="23" t="s">
-        <v>356</v>
+        <v>1329</v>
       </c>
       <c r="F213" s="23" t="s">
         <v>44</v>
@@ -35824,17 +35874,17 @@
         <v>23</v>
       </c>
       <c r="M213" s="23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N213" s="23"/>
       <c r="O213" s="23" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="P213" s="23" t="s">
-        <v>1488</v>
+        <v>1536</v>
       </c>
       <c r="Q213" s="23" t="s">
-        <v>1534</v>
+        <v>1537</v>
       </c>
       <c r="R213" s="23"/>
       <c r="S213" s="23"/>
@@ -35845,7 +35895,7 @@
         <v>345</v>
       </c>
       <c r="V213" s="23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W213" s="23" t="n">
         <v>0</v>
@@ -35871,19 +35921,19 @@
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="23" t="s">
-        <v>1535</v>
+        <v>1538</v>
       </c>
       <c r="B214" s="23" t="s">
-        <v>1536</v>
+        <v>1539</v>
       </c>
       <c r="C214" s="23" t="s">
-        <v>1537</v>
+        <v>1540</v>
       </c>
       <c r="D214" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E214" s="23" t="s">
-        <v>1452</v>
+        <v>1310</v>
       </c>
       <c r="F214" s="23" t="s">
         <v>44</v>
@@ -35905,27 +35955,27 @@
         <v>177</v>
       </c>
       <c r="M214" s="23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N214" s="23"/>
       <c r="O214" s="23" t="s">
-        <v>1538</v>
+        <v>1431</v>
       </c>
       <c r="P214" s="23"/>
       <c r="Q214" s="23" t="s">
-        <v>1539</v>
+        <v>1432</v>
       </c>
       <c r="R214" s="23" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="S214" s="23" t="s">
-        <v>117</v>
+        <v>596</v>
       </c>
       <c r="T214" s="23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U214" s="23" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="V214" s="23" t="n">
         <v>0</v>
@@ -35937,10 +35987,10 @@
         <v>0</v>
       </c>
       <c r="Y214" s="23" t="n">
-        <v>4.4</v>
+        <v>0.5</v>
       </c>
       <c r="Z214" s="23" t="n">
-        <v>2.6</v>
+        <v>7.5</v>
       </c>
       <c r="AA214" s="23" t="n">
         <v>0</v>
@@ -35954,19 +36004,19 @@
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="23" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="B215" s="23" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="C215" s="23" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="D215" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E215" s="23" t="s">
-        <v>1302</v>
+        <v>356</v>
       </c>
       <c r="F215" s="23" t="s">
         <v>44</v>
@@ -35988,17 +36038,17 @@
         <v>23</v>
       </c>
       <c r="M215" s="23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N215" s="23"/>
       <c r="O215" s="23" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="P215" s="23" t="s">
-        <v>912</v>
+        <v>1495</v>
       </c>
       <c r="Q215" s="23" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="R215" s="23"/>
       <c r="S215" s="23"/>
@@ -36009,7 +36059,7 @@
         <v>345</v>
       </c>
       <c r="V215" s="23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W215" s="23" t="n">
         <v>0</v>
@@ -36035,19 +36085,19 @@
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="23" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="B216" s="23" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="C216" s="23" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="D216" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E216" s="23" t="s">
-        <v>1430</v>
+        <v>1452</v>
       </c>
       <c r="F216" s="23" t="s">
         <v>44</v>
@@ -36063,32 +36113,30 @@
         <v>331</v>
       </c>
       <c r="K216" s="23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L216" s="23" t="s">
-        <v>391</v>
+        <v>177</v>
       </c>
       <c r="M216" s="23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N216" s="23"/>
       <c r="O216" s="23" t="s">
-        <v>1549</v>
-      </c>
-      <c r="P216" s="23" t="s">
         <v>1550</v>
       </c>
+      <c r="P216" s="23"/>
       <c r="Q216" s="23" t="s">
         <v>1551</v>
       </c>
       <c r="R216" s="23" t="s">
-        <v>907</v>
+        <v>127</v>
       </c>
       <c r="S216" s="23" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="T216" s="23" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="U216" s="23" t="s">
         <v>1552</v>
@@ -36097,16 +36145,16 @@
         <v>0</v>
       </c>
       <c r="W216" s="23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X216" s="23" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Y216" s="23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Z216" s="23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA216" s="23" t="n">
         <v>0</v>
@@ -36132,7 +36180,7 @@
         <v>1295</v>
       </c>
       <c r="E217" s="23" t="s">
-        <v>1329</v>
+        <v>1302</v>
       </c>
       <c r="F217" s="23" t="s">
         <v>44</v>
@@ -36148,10 +36196,10 @@
         <v>331</v>
       </c>
       <c r="K217" s="23" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="L217" s="23" t="s">
-        <v>177</v>
+        <v>23</v>
       </c>
       <c r="M217" s="23" t="n">
         <v>6</v>
@@ -36160,24 +36208,22 @@
       <c r="O217" s="23" t="s">
         <v>1556</v>
       </c>
-      <c r="P217" s="23"/>
+      <c r="P217" s="23" t="s">
+        <v>912</v>
+      </c>
       <c r="Q217" s="23" t="s">
         <v>1557</v>
       </c>
-      <c r="R217" s="23" t="s">
-        <v>127</v>
-      </c>
-      <c r="S217" s="23" t="s">
-        <v>117</v>
-      </c>
+      <c r="R217" s="23"/>
+      <c r="S217" s="23"/>
       <c r="T217" s="23" t="s">
-        <v>69</v>
+        <v>344</v>
       </c>
       <c r="U217" s="23" t="s">
-        <v>1558</v>
+        <v>345</v>
       </c>
       <c r="V217" s="23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W217" s="23" t="n">
         <v>0</v>
@@ -36186,10 +36232,10 @@
         <v>0</v>
       </c>
       <c r="Y217" s="23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Z217" s="23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA217" s="23" t="n">
         <v>0</v>
@@ -36203,19 +36249,19 @@
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="23" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B218" s="23" t="s">
         <v>1559</v>
       </c>
-      <c r="B218" s="23" t="s">
+      <c r="C218" s="23" t="s">
         <v>1560</v>
-      </c>
-      <c r="C218" s="23" t="s">
-        <v>1561</v>
       </c>
       <c r="D218" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E218" s="23" t="s">
-        <v>356</v>
+        <v>1430</v>
       </c>
       <c r="F218" s="23" t="s">
         <v>44</v>
@@ -36241,16 +36287,16 @@
       </c>
       <c r="N218" s="23"/>
       <c r="O218" s="23" t="s">
+        <v>1561</v>
+      </c>
+      <c r="P218" s="23" t="s">
         <v>1562</v>
       </c>
-      <c r="P218" s="23" t="s">
+      <c r="Q218" s="23" t="s">
         <v>1563</v>
       </c>
-      <c r="Q218" s="23" t="s">
-        <v>1564</v>
-      </c>
       <c r="R218" s="23" t="s">
-        <v>541</v>
+        <v>907</v>
       </c>
       <c r="S218" s="23" t="s">
         <v>131</v>
@@ -36259,7 +36305,7 @@
         <v>68</v>
       </c>
       <c r="U218" s="23" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="V218" s="23" t="n">
         <v>0</v>
@@ -36288,19 +36334,19 @@
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="23" t="s">
+        <v>1565</v>
+      </c>
+      <c r="B219" s="23" t="s">
         <v>1566</v>
       </c>
-      <c r="B219" s="23" t="s">
+      <c r="C219" s="23" t="s">
         <v>1567</v>
-      </c>
-      <c r="C219" s="23" t="s">
-        <v>1568</v>
       </c>
       <c r="D219" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E219" s="23" t="s">
-        <v>390</v>
+        <v>1329</v>
       </c>
       <c r="F219" s="23" t="s">
         <v>44</v>
@@ -36316,34 +36362,36 @@
         <v>331</v>
       </c>
       <c r="K219" s="23" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="L219" s="23" t="s">
-        <v>23</v>
+        <v>177</v>
       </c>
       <c r="M219" s="23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N219" s="23"/>
       <c r="O219" s="23" t="s">
+        <v>1568</v>
+      </c>
+      <c r="P219" s="23"/>
+      <c r="Q219" s="23" t="s">
         <v>1569</v>
       </c>
-      <c r="P219" s="23" t="s">
+      <c r="R219" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="S219" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="T219" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="U219" s="23" t="s">
         <v>1570</v>
       </c>
-      <c r="Q219" s="23" t="s">
-        <v>1571</v>
-      </c>
-      <c r="R219" s="23"/>
-      <c r="S219" s="23"/>
-      <c r="T219" s="23" t="s">
-        <v>344</v>
-      </c>
-      <c r="U219" s="23" t="s">
-        <v>345</v>
-      </c>
       <c r="V219" s="23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W219" s="23" t="n">
         <v>0</v>
@@ -36352,10 +36400,10 @@
         <v>0</v>
       </c>
       <c r="Y219" s="23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Z219" s="23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA219" s="23" t="n">
         <v>0</v>
@@ -36369,19 +36417,19 @@
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="23" t="s">
+        <v>1571</v>
+      </c>
+      <c r="B220" s="23" t="s">
         <v>1572</v>
       </c>
-      <c r="B220" s="23" t="s">
+      <c r="C220" s="23" t="s">
         <v>1573</v>
-      </c>
-      <c r="C220" s="23" t="s">
-        <v>1574</v>
       </c>
       <c r="D220" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E220" s="23" t="s">
-        <v>1430</v>
+        <v>356</v>
       </c>
       <c r="F220" s="23" t="s">
         <v>44</v>
@@ -36403,20 +36451,20 @@
         <v>391</v>
       </c>
       <c r="M220" s="23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N220" s="23"/>
       <c r="O220" s="23" t="s">
+        <v>1574</v>
+      </c>
+      <c r="P220" s="23" t="s">
         <v>1575</v>
       </c>
-      <c r="P220" s="23" t="s">
+      <c r="Q220" s="23" t="s">
         <v>1576</v>
       </c>
-      <c r="Q220" s="23" t="s">
-        <v>1577</v>
-      </c>
       <c r="R220" s="23" t="s">
-        <v>623</v>
+        <v>541</v>
       </c>
       <c r="S220" s="23" t="s">
         <v>131</v>
@@ -36425,16 +36473,16 @@
         <v>68</v>
       </c>
       <c r="U220" s="23" t="s">
-        <v>746</v>
+        <v>1577</v>
       </c>
       <c r="V220" s="23" t="n">
         <v>0</v>
       </c>
       <c r="W220" s="23" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="X220" s="23" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="Y220" s="23" t="n">
         <v>0</v>
@@ -36466,7 +36514,7 @@
         <v>1295</v>
       </c>
       <c r="E221" s="23" t="s">
-        <v>1329</v>
+        <v>390</v>
       </c>
       <c r="F221" s="23" t="s">
         <v>44</v>
@@ -36482,10 +36530,10 @@
         <v>331</v>
       </c>
       <c r="K221" s="23" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="L221" s="23" t="s">
-        <v>391</v>
+        <v>23</v>
       </c>
       <c r="M221" s="23" t="n">
         <v>5</v>
@@ -36495,31 +36543,27 @@
         <v>1581</v>
       </c>
       <c r="P221" s="23" t="s">
-        <v>501</v>
+        <v>1582</v>
       </c>
       <c r="Q221" s="23" t="s">
-        <v>1582</v>
-      </c>
-      <c r="R221" s="23" t="s">
-        <v>336</v>
-      </c>
-      <c r="S221" s="23" t="s">
-        <v>131</v>
-      </c>
+        <v>1583</v>
+      </c>
+      <c r="R221" s="23"/>
+      <c r="S221" s="23"/>
       <c r="T221" s="23" t="s">
-        <v>68</v>
+        <v>344</v>
       </c>
       <c r="U221" s="23" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="V221" s="23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W221" s="23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X221" s="23" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y221" s="23" t="n">
         <v>0</v>
@@ -36539,19 +36583,19 @@
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="23" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="B222" s="23" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="C222" s="23" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="D222" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E222" s="23" t="s">
-        <v>356</v>
+        <v>1430</v>
       </c>
       <c r="F222" s="23" t="s">
         <v>44</v>
@@ -36570,23 +36614,23 @@
         <v>35</v>
       </c>
       <c r="L222" s="23" t="s">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="M222" s="23" t="n">
         <v>5</v>
       </c>
       <c r="N222" s="23"/>
       <c r="O222" s="23" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="P222" s="23" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="Q222" s="23" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="R222" s="23" t="s">
-        <v>439</v>
+        <v>623</v>
       </c>
       <c r="S222" s="23" t="s">
         <v>131</v>
@@ -36595,7 +36639,7 @@
         <v>68</v>
       </c>
       <c r="U222" s="23" t="s">
-        <v>1589</v>
+        <v>746</v>
       </c>
       <c r="V222" s="23" t="n">
         <v>0</v>
@@ -36636,7 +36680,7 @@
         <v>1295</v>
       </c>
       <c r="E223" s="23" t="s">
-        <v>356</v>
+        <v>1329</v>
       </c>
       <c r="F223" s="23" t="s">
         <v>44</v>
@@ -36658,20 +36702,20 @@
         <v>391</v>
       </c>
       <c r="M223" s="23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N223" s="23"/>
       <c r="O223" s="23" t="s">
         <v>1593</v>
       </c>
       <c r="P223" s="23" t="s">
+        <v>501</v>
+      </c>
+      <c r="Q223" s="23" t="s">
         <v>1594</v>
       </c>
-      <c r="Q223" s="23" t="s">
-        <v>1595</v>
-      </c>
       <c r="R223" s="23" t="s">
-        <v>1596</v>
+        <v>336</v>
       </c>
       <c r="S223" s="23" t="s">
         <v>131</v>
@@ -36680,16 +36724,16 @@
         <v>68</v>
       </c>
       <c r="U223" s="23" t="s">
-        <v>1597</v>
+        <v>337</v>
       </c>
       <c r="V223" s="23" t="n">
         <v>0</v>
       </c>
       <c r="W223" s="23" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="X223" s="23" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="Y223" s="23" t="n">
         <v>0</v>
@@ -36709,13 +36753,13 @@
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="23" t="s">
-        <v>1598</v>
+        <v>1595</v>
       </c>
       <c r="B224" s="23" t="s">
-        <v>1599</v>
+        <v>1596</v>
       </c>
       <c r="C224" s="23" t="s">
-        <v>1600</v>
+        <v>1597</v>
       </c>
       <c r="D224" s="23" t="s">
         <v>1295</v>
@@ -36740,23 +36784,23 @@
         <v>35</v>
       </c>
       <c r="L224" s="23" t="s">
-        <v>391</v>
+        <v>370</v>
       </c>
       <c r="M224" s="23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N224" s="23"/>
       <c r="O224" s="23" t="s">
-        <v>1601</v>
+        <v>1598</v>
       </c>
       <c r="P224" s="23" t="s">
-        <v>1602</v>
+        <v>1599</v>
       </c>
       <c r="Q224" s="23" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="R224" s="23" t="s">
-        <v>907</v>
+        <v>439</v>
       </c>
       <c r="S224" s="23" t="s">
         <v>131</v>
@@ -36765,16 +36809,16 @@
         <v>68</v>
       </c>
       <c r="U224" s="23" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="V224" s="23" t="n">
         <v>0</v>
       </c>
       <c r="W224" s="23" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="X224" s="23" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="Y224" s="23" t="n">
         <v>0</v>
@@ -36794,13 +36838,13 @@
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="23" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="B225" s="23" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="C225" s="23" t="s">
-        <v>1607</v>
+        <v>1604</v>
       </c>
       <c r="D225" s="23" t="s">
         <v>1295</v>
@@ -36832,37 +36876,37 @@
       </c>
       <c r="N225" s="23"/>
       <c r="O225" s="23" t="s">
+        <v>1605</v>
+      </c>
+      <c r="P225" s="23" t="s">
+        <v>1606</v>
+      </c>
+      <c r="Q225" s="23" t="s">
+        <v>1607</v>
+      </c>
+      <c r="R225" s="23" t="s">
         <v>1608</v>
       </c>
-      <c r="P225" s="23" t="s">
-        <v>1609</v>
-      </c>
-      <c r="Q225" s="23" t="s">
-        <v>1610</v>
-      </c>
-      <c r="R225" s="23" t="s">
-        <v>920</v>
-      </c>
       <c r="S225" s="23" t="s">
-        <v>410</v>
+        <v>131</v>
       </c>
       <c r="T225" s="23" t="s">
         <v>68</v>
       </c>
       <c r="U225" s="23" t="s">
-        <v>1084</v>
+        <v>1609</v>
       </c>
       <c r="V225" s="23" t="n">
         <v>0</v>
       </c>
       <c r="W225" s="23" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="X225" s="23" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="Y225" s="23" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="Z225" s="23" t="n">
         <v>0</v>
@@ -36879,13 +36923,13 @@
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="23" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B226" s="23" t="s">
         <v>1611</v>
       </c>
-      <c r="B226" s="23" t="s">
+      <c r="C226" s="23" t="s">
         <v>1612</v>
-      </c>
-      <c r="C226" s="23" t="s">
-        <v>1613</v>
       </c>
       <c r="D226" s="23" t="s">
         <v>1295</v>
@@ -36907,40 +36951,44 @@
         <v>331</v>
       </c>
       <c r="K226" s="23" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="L226" s="23" t="s">
-        <v>23</v>
+        <v>391</v>
       </c>
       <c r="M226" s="23" t="n">
         <v>4</v>
       </c>
       <c r="N226" s="23"/>
       <c r="O226" s="23" t="s">
-        <v>1022</v>
+        <v>1613</v>
       </c>
       <c r="P226" s="23" t="s">
         <v>1614</v>
       </c>
       <c r="Q226" s="23" t="s">
-        <v>1024</v>
-      </c>
-      <c r="R226" s="23"/>
-      <c r="S226" s="23"/>
+        <v>1615</v>
+      </c>
+      <c r="R226" s="23" t="s">
+        <v>907</v>
+      </c>
+      <c r="S226" s="23" t="s">
+        <v>131</v>
+      </c>
       <c r="T226" s="23" t="s">
-        <v>344</v>
+        <v>68</v>
       </c>
       <c r="U226" s="23" t="s">
-        <v>345</v>
+        <v>1616</v>
       </c>
       <c r="V226" s="23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W226" s="23" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="X226" s="23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y226" s="23" t="n">
         <v>0</v>
@@ -36960,13 +37008,13 @@
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="23" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="B227" s="23" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="C227" s="23" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="D227" s="23" t="s">
         <v>1295</v>
@@ -36988,43 +37036,47 @@
         <v>331</v>
       </c>
       <c r="K227" s="23" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="L227" s="23" t="s">
-        <v>23</v>
+        <v>391</v>
       </c>
       <c r="M227" s="23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N227" s="23"/>
       <c r="O227" s="23" t="s">
-        <v>1618</v>
+        <v>1620</v>
       </c>
       <c r="P227" s="23" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="Q227" s="23" t="s">
-        <v>1620</v>
-      </c>
-      <c r="R227" s="23"/>
-      <c r="S227" s="23"/>
+        <v>1622</v>
+      </c>
+      <c r="R227" s="23" t="s">
+        <v>920</v>
+      </c>
+      <c r="S227" s="23" t="s">
+        <v>410</v>
+      </c>
       <c r="T227" s="23" t="s">
-        <v>344</v>
+        <v>68</v>
       </c>
       <c r="U227" s="23" t="s">
-        <v>345</v>
+        <v>1084</v>
       </c>
       <c r="V227" s="23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W227" s="23" t="n">
         <v>0</v>
       </c>
       <c r="X227" s="23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y227" s="23" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Z227" s="23" t="n">
         <v>0</v>
@@ -37041,13 +37093,13 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="23" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="B228" s="23" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="C228" s="23" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
       <c r="D228" s="23" t="s">
         <v>1295</v>
@@ -37069,32 +37121,34 @@
         <v>331</v>
       </c>
       <c r="K228" s="23" t="s">
-        <v>105</v>
+        <v>23</v>
       </c>
       <c r="L228" s="23" t="s">
-        <v>177</v>
+        <v>23</v>
       </c>
       <c r="M228" s="23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N228" s="23"/>
       <c r="O228" s="23" t="s">
-        <v>1624</v>
-      </c>
-      <c r="P228" s="23"/>
+        <v>1022</v>
+      </c>
+      <c r="P228" s="23" t="s">
+        <v>1626</v>
+      </c>
       <c r="Q228" s="23" t="s">
-        <v>1625</v>
+        <v>1024</v>
       </c>
       <c r="R228" s="23"/>
       <c r="S228" s="23"/>
       <c r="T228" s="23" t="s">
-        <v>135</v>
+        <v>344</v>
       </c>
       <c r="U228" s="23" t="s">
-        <v>561</v>
+        <v>345</v>
       </c>
       <c r="V228" s="23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W228" s="23" t="n">
         <v>0</v>
@@ -37115,18 +37169,18 @@
         <v>0</v>
       </c>
       <c r="AC228" s="23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="23" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="B229" s="23" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="C229" s="23" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="D229" s="23" t="s">
         <v>1295</v>
@@ -37148,44 +37202,40 @@
         <v>331</v>
       </c>
       <c r="K229" s="23" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="L229" s="23" t="s">
-        <v>370</v>
+        <v>23</v>
       </c>
       <c r="M229" s="23" t="n">
         <v>3</v>
       </c>
       <c r="N229" s="23"/>
       <c r="O229" s="23" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="P229" s="23" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="Q229" s="23" t="s">
-        <v>1631</v>
-      </c>
-      <c r="R229" s="23" t="s">
-        <v>336</v>
-      </c>
-      <c r="S229" s="23" t="s">
-        <v>131</v>
-      </c>
+        <v>1632</v>
+      </c>
+      <c r="R229" s="23"/>
+      <c r="S229" s="23"/>
       <c r="T229" s="23" t="s">
-        <v>68</v>
+        <v>344</v>
       </c>
       <c r="U229" s="23" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="V229" s="23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W229" s="23" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="X229" s="23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y229" s="23" t="n">
         <v>0</v>
@@ -37205,13 +37255,13 @@
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="23" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="B230" s="23" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="C230" s="23" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="D230" s="23" t="s">
         <v>1295</v>
@@ -37233,7 +37283,7 @@
         <v>331</v>
       </c>
       <c r="K230" s="23" t="s">
-        <v>36</v>
+        <v>105</v>
       </c>
       <c r="L230" s="23" t="s">
         <v>177</v>
@@ -37243,23 +37293,19 @@
       </c>
       <c r="N230" s="23"/>
       <c r="O230" s="23" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="P230" s="23"/>
       <c r="Q230" s="23" t="s">
-        <v>1636</v>
-      </c>
-      <c r="R230" s="23" t="s">
-        <v>127</v>
-      </c>
-      <c r="S230" s="23" t="s">
-        <v>117</v>
-      </c>
+        <v>1637</v>
+      </c>
+      <c r="R230" s="23"/>
+      <c r="S230" s="23"/>
       <c r="T230" s="23" t="s">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="U230" s="23" t="s">
-        <v>630</v>
+        <v>561</v>
       </c>
       <c r="V230" s="23" t="n">
         <v>0</v>
@@ -37271,10 +37317,10 @@
         <v>0</v>
       </c>
       <c r="Y230" s="23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z230" s="23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AA230" s="23" t="n">
         <v>0</v>
@@ -37283,24 +37329,24 @@
         <v>0</v>
       </c>
       <c r="AC230" s="23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="23" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="B231" s="23" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="C231" s="23" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="D231" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E231" s="23" t="s">
-        <v>390</v>
+        <v>356</v>
       </c>
       <c r="F231" s="23" t="s">
         <v>44</v>
@@ -37316,40 +37362,44 @@
         <v>331</v>
       </c>
       <c r="K231" s="23" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="L231" s="23" t="s">
-        <v>23</v>
+        <v>370</v>
       </c>
       <c r="M231" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N231" s="23"/>
       <c r="O231" s="23" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="P231" s="23" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="Q231" s="23" t="s">
-        <v>1642</v>
-      </c>
-      <c r="R231" s="23"/>
-      <c r="S231" s="23"/>
+        <v>1643</v>
+      </c>
+      <c r="R231" s="23" t="s">
+        <v>336</v>
+      </c>
+      <c r="S231" s="23" t="s">
+        <v>131</v>
+      </c>
       <c r="T231" s="23" t="s">
-        <v>344</v>
+        <v>68</v>
       </c>
       <c r="U231" s="23" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="V231" s="23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W231" s="23" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="X231" s="23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y231" s="23" t="n">
         <v>0</v>
@@ -37369,13 +37419,13 @@
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="23" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B232" s="23" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="C232" s="23" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="D232" s="23" t="s">
         <v>1295</v>
@@ -37397,50 +37447,48 @@
         <v>331</v>
       </c>
       <c r="K232" s="23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L232" s="23" t="s">
-        <v>370</v>
+        <v>177</v>
       </c>
       <c r="M232" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N232" s="23"/>
       <c r="O232" s="23" t="s">
-        <v>1646</v>
-      </c>
-      <c r="P232" s="23" t="s">
         <v>1647</v>
       </c>
+      <c r="P232" s="23"/>
       <c r="Q232" s="23" t="s">
         <v>1648</v>
       </c>
       <c r="R232" s="23" t="s">
-        <v>1372</v>
+        <v>127</v>
       </c>
       <c r="S232" s="23" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="T232" s="23" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="U232" s="23" t="s">
-        <v>1649</v>
+        <v>630</v>
       </c>
       <c r="V232" s="23" t="n">
         <v>0</v>
       </c>
       <c r="W232" s="23" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X232" s="23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Y232" s="23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z232" s="23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AA232" s="23" t="n">
         <v>0</v>
@@ -37454,19 +37502,19 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="23" t="s">
+        <v>1649</v>
+      </c>
+      <c r="B233" s="23" t="s">
         <v>1650</v>
       </c>
-      <c r="B233" s="23" t="s">
+      <c r="C233" s="23" t="s">
         <v>1651</v>
-      </c>
-      <c r="C233" s="23" t="s">
-        <v>1652</v>
       </c>
       <c r="D233" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E233" s="23" t="s">
-        <v>356</v>
+        <v>390</v>
       </c>
       <c r="F233" s="23" t="s">
         <v>44</v>
@@ -37482,32 +37530,34 @@
         <v>331</v>
       </c>
       <c r="K233" s="23" t="s">
-        <v>105</v>
+        <v>23</v>
       </c>
       <c r="L233" s="23" t="s">
-        <v>177</v>
+        <v>23</v>
       </c>
       <c r="M233" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N233" s="23"/>
       <c r="O233" s="23" t="s">
+        <v>1652</v>
+      </c>
+      <c r="P233" s="23" t="s">
         <v>1653</v>
       </c>
-      <c r="P233" s="23"/>
       <c r="Q233" s="23" t="s">
         <v>1654</v>
       </c>
       <c r="R233" s="23"/>
       <c r="S233" s="23"/>
       <c r="T233" s="23" t="s">
-        <v>135</v>
+        <v>344</v>
       </c>
       <c r="U233" s="23" t="s">
-        <v>561</v>
+        <v>345</v>
       </c>
       <c r="V233" s="23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W233" s="23" t="n">
         <v>0</v>
@@ -37528,7 +37578,7 @@
         <v>0</v>
       </c>
       <c r="AC233" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37552,47 +37602,53 @@
       </c>
       <c r="G234" s="23"/>
       <c r="H234" s="23" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="I234" s="23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J234" s="23" t="s">
         <v>331</v>
       </c>
       <c r="K234" s="23" t="s">
-        <v>105</v>
+        <v>35</v>
       </c>
       <c r="L234" s="23" t="s">
-        <v>460</v>
+        <v>370</v>
       </c>
       <c r="M234" s="23" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="N234" s="23"/>
       <c r="O234" s="23" t="s">
         <v>1658</v>
       </c>
-      <c r="P234" s="23"/>
+      <c r="P234" s="23" t="s">
+        <v>1659</v>
+      </c>
       <c r="Q234" s="23" t="s">
-        <v>1659</v>
-      </c>
-      <c r="R234" s="23"/>
-      <c r="S234" s="23"/>
+        <v>1660</v>
+      </c>
+      <c r="R234" s="23" t="s">
+        <v>1372</v>
+      </c>
+      <c r="S234" s="23" t="s">
+        <v>131</v>
+      </c>
       <c r="T234" s="23" t="s">
-        <v>135</v>
+        <v>68</v>
       </c>
       <c r="U234" s="23" t="s">
-        <v>561</v>
+        <v>1661</v>
       </c>
       <c r="V234" s="23" t="n">
         <v>0</v>
       </c>
       <c r="W234" s="23" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="X234" s="23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y234" s="23" t="n">
         <v>0</v>
@@ -37607,67 +37663,65 @@
         <v>0</v>
       </c>
       <c r="AC234" s="23" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="23" t="s">
-        <v>1660</v>
+        <v>1662</v>
       </c>
       <c r="B235" s="23" t="s">
-        <v>1661</v>
+        <v>1663</v>
       </c>
       <c r="C235" s="23" t="s">
-        <v>1662</v>
+        <v>1664</v>
       </c>
       <c r="D235" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E235" s="23" t="s">
-        <v>1452</v>
+        <v>356</v>
       </c>
       <c r="F235" s="23" t="s">
         <v>44</v>
       </c>
       <c r="G235" s="23"/>
       <c r="H235" s="23" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="I235" s="23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J235" s="23" t="s">
         <v>331</v>
       </c>
       <c r="K235" s="23" t="s">
-        <v>23</v>
+        <v>105</v>
       </c>
       <c r="L235" s="23" t="s">
-        <v>23</v>
+        <v>177</v>
       </c>
       <c r="M235" s="23" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="N235" s="23"/>
       <c r="O235" s="23" t="s">
-        <v>1663</v>
-      </c>
-      <c r="P235" s="23" t="s">
-        <v>1664</v>
-      </c>
+        <v>1665</v>
+      </c>
+      <c r="P235" s="23"/>
       <c r="Q235" s="23" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="R235" s="23"/>
       <c r="S235" s="23"/>
       <c r="T235" s="23" t="s">
-        <v>344</v>
+        <v>135</v>
       </c>
       <c r="U235" s="23" t="s">
-        <v>345</v>
+        <v>561</v>
       </c>
       <c r="V235" s="23" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="W235" s="23" t="n">
         <v>0</v>
@@ -37688,18 +37742,18 @@
         <v>0</v>
       </c>
       <c r="AC235" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="23" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="B236" s="23" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="C236" s="23" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="D236" s="23" t="s">
         <v>1295</v>
@@ -37718,35 +37772,35 @@
         <v>101</v>
       </c>
       <c r="J236" s="23" t="s">
-        <v>436</v>
+        <v>331</v>
       </c>
       <c r="K236" s="23" t="s">
-        <v>23</v>
+        <v>105</v>
       </c>
       <c r="L236" s="23" t="s">
-        <v>23</v>
+        <v>460</v>
       </c>
       <c r="M236" s="23" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="N236" s="23"/>
       <c r="O236" s="23" t="s">
-        <v>1669</v>
-      </c>
-      <c r="P236" s="23" t="s">
-        <v>994</v>
-      </c>
-      <c r="Q236" s="23"/>
+        <v>1670</v>
+      </c>
+      <c r="P236" s="23"/>
+      <c r="Q236" s="23" t="s">
+        <v>1671</v>
+      </c>
       <c r="R236" s="23"/>
       <c r="S236" s="23"/>
       <c r="T236" s="23" t="s">
-        <v>344</v>
+        <v>135</v>
       </c>
       <c r="U236" s="23" t="s">
-        <v>345</v>
+        <v>561</v>
       </c>
       <c r="V236" s="23" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="W236" s="23" t="n">
         <v>0</v>
@@ -37767,24 +37821,24 @@
         <v>0</v>
       </c>
       <c r="AC236" s="23" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="23" t="s">
-        <v>1670</v>
+        <v>1672</v>
       </c>
       <c r="B237" s="23" t="s">
-        <v>1671</v>
+        <v>1673</v>
       </c>
       <c r="C237" s="23" t="s">
-        <v>1672</v>
+        <v>1674</v>
       </c>
       <c r="D237" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E237" s="23" t="s">
-        <v>1323</v>
+        <v>1452</v>
       </c>
       <c r="F237" s="23" t="s">
         <v>44</v>
@@ -37797,35 +37851,37 @@
         <v>101</v>
       </c>
       <c r="J237" s="23" t="s">
-        <v>436</v>
+        <v>331</v>
       </c>
       <c r="K237" s="23" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="L237" s="23" t="s">
-        <v>460</v>
+        <v>23</v>
       </c>
       <c r="M237" s="23" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="N237" s="23"/>
-      <c r="O237" s="23"/>
-      <c r="P237" s="23"/>
-      <c r="Q237" s="23"/>
-      <c r="R237" s="23" t="s">
-        <v>410</v>
-      </c>
-      <c r="S237" s="23" t="s">
-        <v>553</v>
-      </c>
+      <c r="O237" s="23" t="s">
+        <v>1675</v>
+      </c>
+      <c r="P237" s="23" t="s">
+        <v>1676</v>
+      </c>
+      <c r="Q237" s="23" t="s">
+        <v>1677</v>
+      </c>
+      <c r="R237" s="23"/>
+      <c r="S237" s="23"/>
       <c r="T237" s="23" t="s">
-        <v>69</v>
+        <v>344</v>
       </c>
       <c r="U237" s="23" t="s">
-        <v>462</v>
+        <v>345</v>
       </c>
       <c r="V237" s="23" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="W237" s="23" t="n">
         <v>0</v>
@@ -37837,10 +37893,10 @@
         <v>0</v>
       </c>
       <c r="Z237" s="23" t="n">
-        <v>11.3</v>
+        <v>0</v>
       </c>
       <c r="AA237" s="23" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="AB237" s="23" t="n">
         <v>0</v>
@@ -37851,13 +37907,13 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="23" t="s">
-        <v>1673</v>
+        <v>1678</v>
       </c>
       <c r="B238" s="23" t="s">
-        <v>1674</v>
+        <v>1679</v>
       </c>
       <c r="C238" s="23" t="s">
-        <v>1675</v>
+        <v>1680</v>
       </c>
       <c r="D238" s="23" t="s">
         <v>1295</v>
@@ -37876,39 +37932,35 @@
         <v>101</v>
       </c>
       <c r="J238" s="23" t="s">
-        <v>331</v>
+        <v>436</v>
       </c>
       <c r="K238" s="23" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="L238" s="23" t="s">
-        <v>460</v>
+        <v>23</v>
       </c>
       <c r="M238" s="23" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="N238" s="23"/>
       <c r="O238" s="23" t="s">
-        <v>1676</v>
-      </c>
-      <c r="P238" s="23"/>
-      <c r="Q238" s="23" t="s">
-        <v>1677</v>
-      </c>
-      <c r="R238" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="S238" s="23" t="s">
-        <v>365</v>
-      </c>
+        <v>1681</v>
+      </c>
+      <c r="P238" s="23" t="s">
+        <v>994</v>
+      </c>
+      <c r="Q238" s="23"/>
+      <c r="R238" s="23"/>
+      <c r="S238" s="23"/>
       <c r="T238" s="23" t="s">
-        <v>69</v>
+        <v>344</v>
       </c>
       <c r="U238" s="23" t="s">
-        <v>462</v>
+        <v>345</v>
       </c>
       <c r="V238" s="23" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="W238" s="23" t="n">
         <v>0</v>
@@ -37917,10 +37969,10 @@
         <v>0</v>
       </c>
       <c r="Y238" s="23" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="Z238" s="23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA238" s="23" t="n">
         <v>0</v>
@@ -37934,19 +37986,19 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="23" t="s">
-        <v>1678</v>
+        <v>1682</v>
       </c>
       <c r="B239" s="23" t="s">
-        <v>1679</v>
+        <v>1683</v>
       </c>
       <c r="C239" s="23" t="s">
-        <v>1680</v>
+        <v>1684</v>
       </c>
       <c r="D239" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E239" s="23" t="s">
-        <v>356</v>
+        <v>1323</v>
       </c>
       <c r="F239" s="23" t="s">
         <v>44</v>
@@ -37959,37 +38011,35 @@
         <v>101</v>
       </c>
       <c r="J239" s="23" t="s">
-        <v>331</v>
+        <v>436</v>
       </c>
       <c r="K239" s="23" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="L239" s="23" t="s">
-        <v>23</v>
+        <v>460</v>
       </c>
       <c r="M239" s="23" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N239" s="23"/>
-      <c r="O239" s="23" t="s">
-        <v>1681</v>
-      </c>
-      <c r="P239" s="23" t="s">
-        <v>1682</v>
-      </c>
-      <c r="Q239" s="23" t="s">
-        <v>1683</v>
-      </c>
-      <c r="R239" s="23"/>
-      <c r="S239" s="23"/>
+      <c r="O239" s="23"/>
+      <c r="P239" s="23"/>
+      <c r="Q239" s="23"/>
+      <c r="R239" s="23" t="s">
+        <v>410</v>
+      </c>
+      <c r="S239" s="23" t="s">
+        <v>553</v>
+      </c>
       <c r="T239" s="23" t="s">
-        <v>344</v>
+        <v>69</v>
       </c>
       <c r="U239" s="23" t="s">
-        <v>345</v>
+        <v>462</v>
       </c>
       <c r="V239" s="23" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W239" s="23" t="n">
         <v>0</v>
@@ -38001,10 +38051,10 @@
         <v>0</v>
       </c>
       <c r="Z239" s="23" t="n">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="AA239" s="23" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AB239" s="23" t="n">
         <v>0</v>
@@ -38015,13 +38065,13 @@
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="23" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="B240" s="23" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="C240" s="23" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="D240" s="23" t="s">
         <v>1295</v>
@@ -38043,25 +38093,33 @@
         <v>331</v>
       </c>
       <c r="K240" s="23" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="L240" s="23" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="M240" s="23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N240" s="23"/>
-      <c r="O240" s="23"/>
+      <c r="O240" s="23" t="s">
+        <v>1688</v>
+      </c>
       <c r="P240" s="23"/>
-      <c r="Q240" s="23"/>
-      <c r="R240" s="23"/>
-      <c r="S240" s="23"/>
+      <c r="Q240" s="23" t="s">
+        <v>1689</v>
+      </c>
+      <c r="R240" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="S240" s="23" t="s">
+        <v>365</v>
+      </c>
       <c r="T240" s="23" t="s">
-        <v>135</v>
+        <v>69</v>
       </c>
       <c r="U240" s="23" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="V240" s="23" t="n">
         <v>0</v>
@@ -38073,10 +38131,10 @@
         <v>0</v>
       </c>
       <c r="Y240" s="23" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="Z240" s="23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA240" s="23" t="n">
         <v>0</v>
@@ -38085,18 +38143,18 @@
         <v>0</v>
       </c>
       <c r="AC240" s="23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="23" t="s">
-        <v>1687</v>
+        <v>1690</v>
       </c>
       <c r="B241" s="23" t="s">
-        <v>1688</v>
+        <v>1691</v>
       </c>
       <c r="C241" s="23" t="s">
-        <v>1689</v>
+        <v>1692</v>
       </c>
       <c r="D241" s="23" t="s">
         <v>1295</v>
@@ -38118,36 +38176,34 @@
         <v>331</v>
       </c>
       <c r="K241" s="23" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="L241" s="23" t="s">
-        <v>460</v>
+        <v>23</v>
       </c>
       <c r="M241" s="23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N241" s="23"/>
       <c r="O241" s="23" t="s">
-        <v>1690</v>
-      </c>
-      <c r="P241" s="23"/>
+        <v>1693</v>
+      </c>
+      <c r="P241" s="23" t="s">
+        <v>1694</v>
+      </c>
       <c r="Q241" s="23" t="s">
-        <v>1691</v>
-      </c>
-      <c r="R241" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="S241" s="23" t="s">
-        <v>365</v>
-      </c>
+        <v>1695</v>
+      </c>
+      <c r="R241" s="23"/>
+      <c r="S241" s="23"/>
       <c r="T241" s="23" t="s">
-        <v>69</v>
+        <v>344</v>
       </c>
       <c r="U241" s="23" t="s">
-        <v>462</v>
+        <v>345</v>
       </c>
       <c r="V241" s="23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W241" s="23" t="n">
         <v>0</v>
@@ -38156,10 +38212,10 @@
         <v>0</v>
       </c>
       <c r="Y241" s="23" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="Z241" s="23" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="AA241" s="23" t="n">
         <v>0</v>
@@ -38173,59 +38229,53 @@
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="23" t="s">
-        <v>1692</v>
+        <v>1696</v>
       </c>
       <c r="B242" s="23" t="s">
-        <v>1693</v>
+        <v>1697</v>
       </c>
       <c r="C242" s="23" t="s">
-        <v>1694</v>
+        <v>1698</v>
       </c>
       <c r="D242" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E242" s="23" t="s">
-        <v>1302</v>
+        <v>356</v>
       </c>
       <c r="F242" s="23" t="s">
         <v>44</v>
       </c>
       <c r="G242" s="23"/>
       <c r="H242" s="23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I242" s="23" t="s">
         <v>101</v>
       </c>
       <c r="J242" s="23" t="s">
-        <v>436</v>
+        <v>331</v>
       </c>
       <c r="K242" s="23" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="L242" s="23" t="s">
-        <v>177</v>
+        <v>466</v>
       </c>
       <c r="M242" s="23" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="N242" s="23"/>
-      <c r="O242" s="23" t="s">
-        <v>1695</v>
-      </c>
+      <c r="O242" s="23"/>
       <c r="P242" s="23"/>
       <c r="Q242" s="23"/>
-      <c r="R242" s="23" t="s">
-        <v>127</v>
-      </c>
-      <c r="S242" s="23" t="s">
-        <v>365</v>
-      </c>
+      <c r="R242" s="23"/>
+      <c r="S242" s="23"/>
       <c r="T242" s="23" t="s">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="U242" s="23" t="s">
-        <v>1411</v>
+        <v>467</v>
       </c>
       <c r="V242" s="23" t="n">
         <v>0</v>
@@ -38237,10 +38287,10 @@
         <v>0</v>
       </c>
       <c r="Y242" s="23" t="n">
-        <v>23.6</v>
+        <v>0</v>
       </c>
       <c r="Z242" s="23" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AA242" s="23" t="n">
         <v>0</v>
@@ -38249,64 +38299,66 @@
         <v>0</v>
       </c>
       <c r="AC242" s="23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="23" t="s">
-        <v>1696</v>
+        <v>1699</v>
       </c>
       <c r="B243" s="23" t="s">
-        <v>1697</v>
+        <v>1700</v>
       </c>
       <c r="C243" s="23" t="s">
-        <v>1698</v>
+        <v>1701</v>
       </c>
       <c r="D243" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E243" s="23" t="s">
-        <v>1296</v>
+        <v>356</v>
       </c>
       <c r="F243" s="23" t="s">
         <v>44</v>
       </c>
       <c r="G243" s="23"/>
       <c r="H243" s="23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I243" s="23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J243" s="23" t="s">
-        <v>436</v>
+        <v>331</v>
       </c>
       <c r="K243" s="23" t="s">
         <v>36</v>
       </c>
       <c r="L243" s="23" t="s">
-        <v>177</v>
+        <v>460</v>
       </c>
       <c r="M243" s="23" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="N243" s="23"/>
       <c r="O243" s="23" t="s">
-        <v>1699</v>
+        <v>1702</v>
       </c>
       <c r="P243" s="23"/>
-      <c r="Q243" s="23"/>
+      <c r="Q243" s="23" t="s">
+        <v>1703</v>
+      </c>
       <c r="R243" s="23" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="S243" s="23" t="s">
         <v>365</v>
       </c>
       <c r="T243" s="23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U243" s="23" t="s">
-        <v>1700</v>
+        <v>462</v>
       </c>
       <c r="V243" s="23" t="n">
         <v>0</v>
@@ -38318,10 +38370,10 @@
         <v>0</v>
       </c>
       <c r="Y243" s="23" t="n">
-        <v>23.6</v>
+        <v>6.1</v>
       </c>
       <c r="Z243" s="23" t="n">
-        <v>7.4</v>
+        <v>0.9</v>
       </c>
       <c r="AA243" s="23" t="n">
         <v>0</v>
@@ -38335,19 +38387,19 @@
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="23" t="s">
-        <v>1701</v>
+        <v>1704</v>
       </c>
       <c r="B244" s="23" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
       <c r="C244" s="23" t="s">
-        <v>1703</v>
+        <v>1706</v>
       </c>
       <c r="D244" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E244" s="23" t="s">
-        <v>1329</v>
+        <v>1302</v>
       </c>
       <c r="F244" s="23" t="s">
         <v>44</v>
@@ -38363,33 +38415,31 @@
         <v>436</v>
       </c>
       <c r="K244" s="23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L244" s="23" t="s">
-        <v>391</v>
+        <v>177</v>
       </c>
       <c r="M244" s="23" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="N244" s="23"/>
       <c r="O244" s="23" t="s">
-        <v>1704</v>
-      </c>
-      <c r="P244" s="23" t="s">
-        <v>1705</v>
-      </c>
+        <v>1707</v>
+      </c>
+      <c r="P244" s="23"/>
       <c r="Q244" s="23"/>
       <c r="R244" s="23" t="s">
-        <v>736</v>
+        <v>127</v>
       </c>
       <c r="S244" s="23" t="s">
-        <v>117</v>
+        <v>365</v>
       </c>
       <c r="T244" s="23" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="U244" s="23" t="s">
-        <v>737</v>
+        <v>1411</v>
       </c>
       <c r="V244" s="23" t="n">
         <v>0</v>
@@ -38398,13 +38448,13 @@
         <v>0</v>
       </c>
       <c r="X244" s="23" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="Y244" s="23" t="n">
-        <v>12.8</v>
+        <v>23.6</v>
       </c>
       <c r="Z244" s="23" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="AA244" s="23" t="n">
         <v>0</v>
@@ -38418,19 +38468,19 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="23" t="s">
-        <v>1706</v>
+        <v>1708</v>
       </c>
       <c r="B245" s="23" t="s">
-        <v>1707</v>
+        <v>1709</v>
       </c>
       <c r="C245" s="23" t="s">
-        <v>1708</v>
+        <v>1710</v>
       </c>
       <c r="D245" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E245" s="23" t="s">
-        <v>1329</v>
+        <v>1296</v>
       </c>
       <c r="F245" s="23" t="s">
         <v>44</v>
@@ -38440,7 +38490,7 @@
         <v>50</v>
       </c>
       <c r="I245" s="23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J245" s="23" t="s">
         <v>436</v>
@@ -38452,11 +38502,11 @@
         <v>177</v>
       </c>
       <c r="M245" s="23" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="N245" s="23"/>
       <c r="O245" s="23" t="s">
-        <v>1709</v>
+        <v>1711</v>
       </c>
       <c r="P245" s="23"/>
       <c r="Q245" s="23"/>
@@ -38464,13 +38514,13 @@
         <v>127</v>
       </c>
       <c r="S245" s="23" t="s">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="T245" s="23" t="s">
         <v>70</v>
       </c>
       <c r="U245" s="23" t="s">
-        <v>1710</v>
+        <v>1712</v>
       </c>
       <c r="V245" s="23" t="n">
         <v>0</v>
@@ -38482,13 +38532,13 @@
         <v>0</v>
       </c>
       <c r="Y245" s="23" t="n">
-        <v>6.2</v>
+        <v>23.6</v>
       </c>
       <c r="Z245" s="23" t="n">
-        <v>12.8</v>
+        <v>7.4</v>
       </c>
       <c r="AA245" s="23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB245" s="23" t="n">
         <v>0</v>
@@ -38499,13 +38549,13 @@
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="23" t="s">
-        <v>1711</v>
+        <v>1713</v>
       </c>
       <c r="B246" s="23" t="s">
-        <v>1712</v>
+        <v>1714</v>
       </c>
       <c r="C246" s="23" t="s">
-        <v>1713</v>
+        <v>1715</v>
       </c>
       <c r="D246" s="23" t="s">
         <v>1295</v>
@@ -38537,21 +38587,23 @@
       </c>
       <c r="N246" s="23"/>
       <c r="O246" s="23" t="s">
-        <v>1714</v>
-      </c>
-      <c r="P246" s="23"/>
+        <v>1716</v>
+      </c>
+      <c r="P246" s="23" t="s">
+        <v>1717</v>
+      </c>
       <c r="Q246" s="23"/>
       <c r="R246" s="23" t="s">
-        <v>1715</v>
+        <v>736</v>
       </c>
       <c r="S246" s="23" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="T246" s="23" t="s">
         <v>68</v>
       </c>
       <c r="U246" s="23" t="s">
-        <v>1716</v>
+        <v>737</v>
       </c>
       <c r="V246" s="23" t="n">
         <v>0</v>
@@ -38560,13 +38612,13 @@
         <v>0</v>
       </c>
       <c r="X246" s="23" t="n">
-        <v>3</v>
+        <v>5.9</v>
       </c>
       <c r="Y246" s="23" t="n">
         <v>12.8</v>
       </c>
       <c r="Z246" s="23" t="n">
-        <v>8.2</v>
+        <v>5.3</v>
       </c>
       <c r="AA246" s="23" t="n">
         <v>0</v>
@@ -38580,19 +38632,19 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="23" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="B247" s="23" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="C247" s="23" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="D247" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E247" s="23" t="s">
-        <v>356</v>
+        <v>1329</v>
       </c>
       <c r="F247" s="23" t="s">
         <v>44</v>
@@ -38608,32 +38660,34 @@
         <v>436</v>
       </c>
       <c r="K247" s="23" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="L247" s="23" t="s">
-        <v>23</v>
+        <v>177</v>
       </c>
       <c r="M247" s="23" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="N247" s="23"/>
       <c r="O247" s="23" t="s">
-        <v>1720</v>
-      </c>
-      <c r="P247" s="23" t="s">
-        <v>1640</v>
-      </c>
+        <v>1721</v>
+      </c>
+      <c r="P247" s="23"/>
       <c r="Q247" s="23"/>
-      <c r="R247" s="23"/>
-      <c r="S247" s="23"/>
+      <c r="R247" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="S247" s="23" t="s">
+        <v>385</v>
+      </c>
       <c r="T247" s="23" t="s">
-        <v>344</v>
+        <v>70</v>
       </c>
       <c r="U247" s="23" t="s">
-        <v>345</v>
+        <v>1722</v>
       </c>
       <c r="V247" s="23" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="W247" s="23" t="n">
         <v>0</v>
@@ -38642,13 +38696,13 @@
         <v>0</v>
       </c>
       <c r="Y247" s="23" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="Z247" s="23" t="n">
-        <v>0</v>
+        <v>12.8</v>
       </c>
       <c r="AA247" s="23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB247" s="23" t="n">
         <v>0</v>
@@ -38659,19 +38713,19 @@
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="23" t="s">
-        <v>1721</v>
+        <v>1723</v>
       </c>
       <c r="B248" s="23" t="s">
-        <v>1722</v>
+        <v>1724</v>
       </c>
       <c r="C248" s="23" t="s">
-        <v>1723</v>
+        <v>1725</v>
       </c>
       <c r="D248" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E248" s="23" t="s">
-        <v>356</v>
+        <v>1329</v>
       </c>
       <c r="F248" s="23" t="s">
         <v>44</v>
@@ -38687,31 +38741,31 @@
         <v>436</v>
       </c>
       <c r="K248" s="23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L248" s="23" t="s">
-        <v>177</v>
+        <v>391</v>
       </c>
       <c r="M248" s="23" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="N248" s="23"/>
       <c r="O248" s="23" t="s">
-        <v>1724</v>
+        <v>1726</v>
       </c>
       <c r="P248" s="23"/>
       <c r="Q248" s="23"/>
       <c r="R248" s="23" t="s">
-        <v>127</v>
+        <v>1727</v>
       </c>
       <c r="S248" s="23" t="s">
         <v>132</v>
       </c>
       <c r="T248" s="23" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="U248" s="23" t="s">
-        <v>1725</v>
+        <v>1728</v>
       </c>
       <c r="V248" s="23" t="n">
         <v>0</v>
@@ -38720,13 +38774,13 @@
         <v>0</v>
       </c>
       <c r="X248" s="23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y248" s="23" t="n">
-        <v>7.5</v>
+        <v>12.8</v>
       </c>
       <c r="Z248" s="23" t="n">
-        <v>10.5</v>
+        <v>8.2</v>
       </c>
       <c r="AA248" s="23" t="n">
         <v>0</v>
@@ -38740,19 +38794,19 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="23" t="s">
-        <v>1726</v>
+        <v>1729</v>
       </c>
       <c r="B249" s="23" t="s">
-        <v>1727</v>
+        <v>1730</v>
       </c>
       <c r="C249" s="23" t="s">
-        <v>1728</v>
+        <v>1731</v>
       </c>
       <c r="D249" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E249" s="23" t="s">
-        <v>1310</v>
+        <v>356</v>
       </c>
       <c r="F249" s="23" t="s">
         <v>44</v>
@@ -38768,45 +38822,41 @@
         <v>436</v>
       </c>
       <c r="K249" s="23" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="L249" s="23" t="s">
-        <v>391</v>
+        <v>23</v>
       </c>
       <c r="M249" s="23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N249" s="23"/>
       <c r="O249" s="23" t="s">
-        <v>1729</v>
+        <v>1732</v>
       </c>
       <c r="P249" s="23" t="s">
-        <v>1730</v>
+        <v>1652</v>
       </c>
       <c r="Q249" s="23"/>
-      <c r="R249" s="23" t="s">
-        <v>409</v>
-      </c>
-      <c r="S249" s="23" t="s">
-        <v>577</v>
-      </c>
+      <c r="R249" s="23"/>
+      <c r="S249" s="23"/>
       <c r="T249" s="23" t="s">
-        <v>68</v>
+        <v>344</v>
       </c>
       <c r="U249" s="23" t="s">
-        <v>642</v>
+        <v>345</v>
       </c>
       <c r="V249" s="23" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="W249" s="23" t="n">
         <v>0</v>
       </c>
       <c r="X249" s="23" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="Y249" s="23" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="Z249" s="23" t="n">
         <v>0</v>
@@ -38823,13 +38873,13 @@
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="23" t="s">
-        <v>1731</v>
+        <v>1733</v>
       </c>
       <c r="B250" s="23" t="s">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="C250" s="23" t="s">
-        <v>1733</v>
+        <v>1735</v>
       </c>
       <c r="D250" s="23" t="s">
         <v>1295</v>
@@ -38851,48 +38901,46 @@
         <v>436</v>
       </c>
       <c r="K250" s="23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L250" s="23" t="s">
-        <v>332</v>
+        <v>177</v>
       </c>
       <c r="M250" s="23" t="n">
         <v>18</v>
       </c>
       <c r="N250" s="23"/>
       <c r="O250" s="23" t="s">
-        <v>1734</v>
-      </c>
-      <c r="P250" s="23" t="s">
-        <v>1735</v>
-      </c>
+        <v>1736</v>
+      </c>
+      <c r="P250" s="23"/>
       <c r="Q250" s="23"/>
       <c r="R250" s="23" t="s">
-        <v>1076</v>
+        <v>127</v>
       </c>
       <c r="S250" s="23" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="T250" s="23" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="U250" s="23" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="V250" s="23" t="n">
         <v>0</v>
       </c>
       <c r="W250" s="23" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="X250" s="23" t="n">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="Y250" s="23" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Z250" s="23" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AA250" s="23" t="n">
         <v>0</v>
@@ -38906,19 +38954,19 @@
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="23" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="B251" s="23" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="C251" s="23" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="D251" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E251" s="23" t="s">
-        <v>1329</v>
+        <v>1310</v>
       </c>
       <c r="F251" s="23" t="s">
         <v>44</v>
@@ -38937,42 +38985,42 @@
         <v>35</v>
       </c>
       <c r="L251" s="23" t="s">
-        <v>449</v>
+        <v>391</v>
       </c>
       <c r="M251" s="23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N251" s="23"/>
       <c r="O251" s="23" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="P251" s="23" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="Q251" s="23"/>
       <c r="R251" s="23" t="s">
-        <v>451</v>
+        <v>409</v>
       </c>
       <c r="S251" s="23" t="s">
-        <v>131</v>
+        <v>577</v>
       </c>
       <c r="T251" s="23" t="s">
         <v>68</v>
       </c>
       <c r="U251" s="23" t="s">
-        <v>1742</v>
+        <v>642</v>
       </c>
       <c r="V251" s="23" t="n">
         <v>0</v>
       </c>
       <c r="W251" s="23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="X251" s="23" t="n">
-        <v>12.3</v>
+        <v>10.2</v>
       </c>
       <c r="Y251" s="23" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="Z251" s="23" t="n">
         <v>0</v>
@@ -39014,29 +39062,27 @@
         <v>101</v>
       </c>
       <c r="J252" s="23" t="s">
-        <v>331</v>
+        <v>436</v>
       </c>
       <c r="K252" s="23" t="s">
         <v>35</v>
       </c>
       <c r="L252" s="23" t="s">
-        <v>391</v>
+        <v>332</v>
       </c>
       <c r="M252" s="23" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="N252" s="23"/>
       <c r="O252" s="23" t="s">
-        <v>1336</v>
+        <v>1746</v>
       </c>
       <c r="P252" s="23" t="s">
-        <v>849</v>
-      </c>
-      <c r="Q252" s="23" t="s">
-        <v>1746</v>
-      </c>
+        <v>1747</v>
+      </c>
+      <c r="Q252" s="23"/>
       <c r="R252" s="23" t="s">
-        <v>336</v>
+        <v>1076</v>
       </c>
       <c r="S252" s="23" t="s">
         <v>131</v>
@@ -39045,16 +39091,16 @@
         <v>68</v>
       </c>
       <c r="U252" s="23" t="s">
-        <v>337</v>
+        <v>1748</v>
       </c>
       <c r="V252" s="23" t="n">
         <v>0</v>
       </c>
       <c r="W252" s="23" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="X252" s="23" t="n">
-        <v>10.7</v>
+        <v>13.8</v>
       </c>
       <c r="Y252" s="23" t="n">
         <v>0</v>
@@ -39074,19 +39120,19 @@
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="23" t="s">
-        <v>1747</v>
+        <v>1749</v>
       </c>
       <c r="B253" s="23" t="s">
-        <v>1748</v>
+        <v>1750</v>
       </c>
       <c r="C253" s="23" t="s">
-        <v>1049</v>
+        <v>1751</v>
       </c>
       <c r="D253" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E253" s="23" t="s">
-        <v>356</v>
+        <v>1329</v>
       </c>
       <c r="F253" s="23" t="s">
         <v>44</v>
@@ -39102,38 +39148,42 @@
         <v>436</v>
       </c>
       <c r="K253" s="23" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="L253" s="23" t="s">
-        <v>23</v>
+        <v>449</v>
       </c>
       <c r="M253" s="23" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N253" s="23"/>
       <c r="O253" s="23" t="s">
-        <v>1749</v>
+        <v>1752</v>
       </c>
       <c r="P253" s="23" t="s">
-        <v>1750</v>
+        <v>1753</v>
       </c>
       <c r="Q253" s="23"/>
-      <c r="R253" s="23"/>
-      <c r="S253" s="23"/>
+      <c r="R253" s="23" t="s">
+        <v>451</v>
+      </c>
+      <c r="S253" s="23" t="s">
+        <v>131</v>
+      </c>
       <c r="T253" s="23" t="s">
-        <v>344</v>
+        <v>68</v>
       </c>
       <c r="U253" s="23" t="s">
-        <v>345</v>
+        <v>1754</v>
       </c>
       <c r="V253" s="23" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="W253" s="23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="X253" s="23" t="n">
-        <v>0</v>
+        <v>12.3</v>
       </c>
       <c r="Y253" s="23" t="n">
         <v>0</v>
@@ -39153,13 +39203,13 @@
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="23" t="s">
-        <v>1751</v>
+        <v>1755</v>
       </c>
       <c r="B254" s="23" t="s">
-        <v>1752</v>
+        <v>1756</v>
       </c>
       <c r="C254" s="23" t="s">
-        <v>1753</v>
+        <v>1757</v>
       </c>
       <c r="D254" s="23" t="s">
         <v>1295</v>
@@ -39178,49 +39228,53 @@
         <v>101</v>
       </c>
       <c r="J254" s="23" t="s">
-        <v>436</v>
+        <v>331</v>
       </c>
       <c r="K254" s="23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L254" s="23" t="s">
-        <v>177</v>
+        <v>391</v>
       </c>
       <c r="M254" s="23" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N254" s="23"/>
       <c r="O254" s="23" t="s">
-        <v>471</v>
-      </c>
-      <c r="P254" s="23"/>
-      <c r="Q254" s="23"/>
+        <v>1336</v>
+      </c>
+      <c r="P254" s="23" t="s">
+        <v>849</v>
+      </c>
+      <c r="Q254" s="23" t="s">
+        <v>1758</v>
+      </c>
       <c r="R254" s="23" t="s">
-        <v>127</v>
+        <v>336</v>
       </c>
       <c r="S254" s="23" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="T254" s="23" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="U254" s="23" t="s">
-        <v>1754</v>
+        <v>337</v>
       </c>
       <c r="V254" s="23" t="n">
         <v>0</v>
       </c>
       <c r="W254" s="23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X254" s="23" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="Y254" s="23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z254" s="23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA254" s="23" t="n">
         <v>0</v>
@@ -39234,19 +39288,19 @@
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="23" t="s">
-        <v>1755</v>
+        <v>1759</v>
       </c>
       <c r="B255" s="23" t="s">
-        <v>1756</v>
+        <v>1760</v>
       </c>
       <c r="C255" s="23" t="s">
-        <v>1757</v>
+        <v>1049</v>
       </c>
       <c r="D255" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E255" s="23" t="s">
-        <v>1296</v>
+        <v>356</v>
       </c>
       <c r="F255" s="23" t="s">
         <v>44</v>
@@ -39262,40 +39316,38 @@
         <v>436</v>
       </c>
       <c r="K255" s="23" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="L255" s="23" t="s">
-        <v>391</v>
+        <v>23</v>
       </c>
       <c r="M255" s="23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N255" s="23"/>
-      <c r="O255" s="23"/>
+      <c r="O255" s="23" t="s">
+        <v>1761</v>
+      </c>
       <c r="P255" s="23" t="s">
-        <v>1758</v>
+        <v>1762</v>
       </c>
       <c r="Q255" s="23"/>
-      <c r="R255" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="S255" s="23" t="s">
-        <v>131</v>
-      </c>
+      <c r="R255" s="23"/>
+      <c r="S255" s="23"/>
       <c r="T255" s="23" t="s">
-        <v>68</v>
+        <v>344</v>
       </c>
       <c r="U255" s="23" t="s">
-        <v>1759</v>
+        <v>345</v>
       </c>
       <c r="V255" s="23" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W255" s="23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="X255" s="23" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="Y255" s="23" t="n">
         <v>0</v>
@@ -39315,13 +39367,13 @@
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="23" t="s">
-        <v>1760</v>
+        <v>1763</v>
       </c>
       <c r="B256" s="23" t="s">
-        <v>1761</v>
+        <v>1764</v>
       </c>
       <c r="C256" s="23" t="s">
-        <v>1762</v>
+        <v>1765</v>
       </c>
       <c r="D256" s="23" t="s">
         <v>1295</v>
@@ -39343,32 +39395,34 @@
         <v>436</v>
       </c>
       <c r="K256" s="23" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="L256" s="23" t="s">
-        <v>23</v>
+        <v>177</v>
       </c>
       <c r="M256" s="23" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N256" s="23"/>
       <c r="O256" s="23" t="s">
-        <v>1763</v>
-      </c>
-      <c r="P256" s="23" t="s">
-        <v>1764</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="P256" s="23"/>
       <c r="Q256" s="23"/>
-      <c r="R256" s="23"/>
-      <c r="S256" s="23"/>
+      <c r="R256" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="S256" s="23" t="s">
+        <v>117</v>
+      </c>
       <c r="T256" s="23" t="s">
-        <v>344</v>
+        <v>70</v>
       </c>
       <c r="U256" s="23" t="s">
-        <v>345</v>
+        <v>1766</v>
       </c>
       <c r="V256" s="23" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W256" s="23" t="n">
         <v>0</v>
@@ -39377,10 +39431,10 @@
         <v>0</v>
       </c>
       <c r="Y256" s="23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z256" s="23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA256" s="23" t="n">
         <v>0</v>
@@ -39394,19 +39448,19 @@
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="23" t="s">
-        <v>1765</v>
+        <v>1767</v>
       </c>
       <c r="B257" s="23" t="s">
-        <v>1766</v>
+        <v>1768</v>
       </c>
       <c r="C257" s="23" t="s">
-        <v>1767</v>
+        <v>1769</v>
       </c>
       <c r="D257" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E257" s="23" t="s">
-        <v>356</v>
+        <v>1296</v>
       </c>
       <c r="F257" s="23" t="s">
         <v>44</v>
@@ -39428,18 +39482,16 @@
         <v>391</v>
       </c>
       <c r="M257" s="23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N257" s="23"/>
-      <c r="O257" s="23" t="s">
-        <v>602</v>
-      </c>
+      <c r="O257" s="23"/>
       <c r="P257" s="23" t="s">
-        <v>1768</v>
+        <v>1770</v>
       </c>
       <c r="Q257" s="23"/>
       <c r="R257" s="23" t="s">
-        <v>959</v>
+        <v>124</v>
       </c>
       <c r="S257" s="23" t="s">
         <v>131</v>
@@ -39448,16 +39500,16 @@
         <v>68</v>
       </c>
       <c r="U257" s="23" t="s">
-        <v>1183</v>
+        <v>1771</v>
       </c>
       <c r="V257" s="23" t="n">
         <v>0</v>
       </c>
       <c r="W257" s="23" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="X257" s="23" t="n">
-        <v>7.7</v>
+        <v>8.4</v>
       </c>
       <c r="Y257" s="23" t="n">
         <v>0</v>
@@ -39477,13 +39529,13 @@
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="23" t="s">
-        <v>1769</v>
+        <v>1772</v>
       </c>
       <c r="B258" s="23" t="s">
-        <v>1770</v>
+        <v>1773</v>
       </c>
       <c r="C258" s="23" t="s">
-        <v>1771</v>
+        <v>1774</v>
       </c>
       <c r="D258" s="23" t="s">
         <v>1295</v>
@@ -39505,42 +39557,38 @@
         <v>436</v>
       </c>
       <c r="K258" s="23" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="L258" s="23" t="s">
-        <v>391</v>
+        <v>23</v>
       </c>
       <c r="M258" s="23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N258" s="23"/>
       <c r="O258" s="23" t="s">
-        <v>1772</v>
+        <v>1775</v>
       </c>
       <c r="P258" s="23" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="Q258" s="23"/>
-      <c r="R258" s="23" t="s">
-        <v>1076</v>
-      </c>
-      <c r="S258" s="23" t="s">
-        <v>131</v>
-      </c>
+      <c r="R258" s="23"/>
+      <c r="S258" s="23"/>
       <c r="T258" s="23" t="s">
-        <v>68</v>
+        <v>344</v>
       </c>
       <c r="U258" s="23" t="s">
-        <v>1774</v>
+        <v>345</v>
       </c>
       <c r="V258" s="23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W258" s="23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="X258" s="23" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="Y258" s="23" t="n">
         <v>0</v>
@@ -39560,19 +39608,19 @@
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="23" t="s">
-        <v>1775</v>
+        <v>1777</v>
       </c>
       <c r="B259" s="23" t="s">
-        <v>1776</v>
+        <v>1778</v>
       </c>
       <c r="C259" s="23" t="s">
-        <v>1777</v>
+        <v>1779</v>
       </c>
       <c r="D259" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E259" s="23" t="s">
-        <v>1323</v>
+        <v>356</v>
       </c>
       <c r="F259" s="23" t="s">
         <v>44</v>
@@ -39588,46 +39636,48 @@
         <v>436</v>
       </c>
       <c r="K259" s="23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L259" s="23" t="s">
-        <v>177</v>
+        <v>391</v>
       </c>
       <c r="M259" s="23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N259" s="23"/>
       <c r="O259" s="23" t="s">
-        <v>1778</v>
-      </c>
-      <c r="P259" s="23"/>
+        <v>602</v>
+      </c>
+      <c r="P259" s="23" t="s">
+        <v>1780</v>
+      </c>
       <c r="Q259" s="23"/>
       <c r="R259" s="23" t="s">
-        <v>127</v>
+        <v>959</v>
       </c>
       <c r="S259" s="23" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="T259" s="23" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="U259" s="23" t="s">
-        <v>1779</v>
+        <v>1183</v>
       </c>
       <c r="V259" s="23" t="n">
         <v>0</v>
       </c>
       <c r="W259" s="23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X259" s="23" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Y259" s="23" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Z259" s="23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA259" s="23" t="n">
         <v>0</v>
@@ -39641,13 +39691,13 @@
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="23" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="B260" s="23" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="C260" s="23" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="D260" s="23" t="s">
         <v>1295</v>
@@ -39666,43 +39716,45 @@
         <v>101</v>
       </c>
       <c r="J260" s="23" t="s">
-        <v>331</v>
+        <v>436</v>
       </c>
       <c r="K260" s="23" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="L260" s="23" t="s">
-        <v>23</v>
+        <v>391</v>
       </c>
       <c r="M260" s="23" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N260" s="23"/>
       <c r="O260" s="23" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="P260" s="23" t="s">
-        <v>1784</v>
-      </c>
-      <c r="Q260" s="23" t="s">
         <v>1785</v>
       </c>
-      <c r="R260" s="23"/>
-      <c r="S260" s="23"/>
+      <c r="Q260" s="23"/>
+      <c r="R260" s="23" t="s">
+        <v>1076</v>
+      </c>
+      <c r="S260" s="23" t="s">
+        <v>131</v>
+      </c>
       <c r="T260" s="23" t="s">
-        <v>344</v>
+        <v>68</v>
       </c>
       <c r="U260" s="23" t="s">
-        <v>345</v>
+        <v>1786</v>
       </c>
       <c r="V260" s="23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W260" s="23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X260" s="23" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="Y260" s="23" t="n">
         <v>0</v>
@@ -39722,19 +39774,19 @@
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="23" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="B261" s="23" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="C261" s="23" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="D261" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E261" s="23" t="s">
-        <v>1317</v>
+        <v>1323</v>
       </c>
       <c r="F261" s="23" t="s">
         <v>44</v>
@@ -39750,48 +39802,46 @@
         <v>436</v>
       </c>
       <c r="K261" s="23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L261" s="23" t="s">
-        <v>460</v>
+        <v>177</v>
       </c>
       <c r="M261" s="23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N261" s="23"/>
       <c r="O261" s="23" t="s">
-        <v>1290</v>
-      </c>
-      <c r="P261" s="23" t="s">
-        <v>1789</v>
-      </c>
+        <v>1790</v>
+      </c>
+      <c r="P261" s="23"/>
       <c r="Q261" s="23"/>
       <c r="R261" s="23" t="s">
-        <v>1096</v>
+        <v>127</v>
       </c>
       <c r="S261" s="23" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="T261" s="23" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="U261" s="23" t="s">
-        <v>1097</v>
+        <v>1791</v>
       </c>
       <c r="V261" s="23" t="n">
         <v>0</v>
       </c>
       <c r="W261" s="23" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="X261" s="23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y261" s="23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Z261" s="23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA261" s="23" t="n">
         <v>0</v>
@@ -39805,13 +39855,13 @@
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="23" t="s">
-        <v>1790</v>
+        <v>1792</v>
       </c>
       <c r="B262" s="23" t="s">
-        <v>1791</v>
+        <v>1793</v>
       </c>
       <c r="C262" s="23" t="s">
-        <v>1792</v>
+        <v>1794</v>
       </c>
       <c r="D262" s="23" t="s">
         <v>1295</v>
@@ -39830,37 +39880,37 @@
         <v>101</v>
       </c>
       <c r="J262" s="23" t="s">
-        <v>436</v>
+        <v>331</v>
       </c>
       <c r="K262" s="23" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="L262" s="23" t="s">
-        <v>460</v>
+        <v>23</v>
       </c>
       <c r="M262" s="23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N262" s="23"/>
       <c r="O262" s="23" t="s">
-        <v>790</v>
-      </c>
-      <c r="P262" s="23"/>
-      <c r="Q262" s="23"/>
-      <c r="R262" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="S262" s="23" t="s">
-        <v>365</v>
-      </c>
+        <v>1795</v>
+      </c>
+      <c r="P262" s="23" t="s">
+        <v>1796</v>
+      </c>
+      <c r="Q262" s="23" t="s">
+        <v>1797</v>
+      </c>
+      <c r="R262" s="23"/>
+      <c r="S262" s="23"/>
       <c r="T262" s="23" t="s">
-        <v>69</v>
+        <v>344</v>
       </c>
       <c r="U262" s="23" t="s">
-        <v>462</v>
+        <v>345</v>
       </c>
       <c r="V262" s="23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W262" s="23" t="n">
         <v>0</v>
@@ -39869,10 +39919,10 @@
         <v>0</v>
       </c>
       <c r="Y262" s="23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Z262" s="23" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AA262" s="23" t="n">
         <v>0</v>
@@ -39886,19 +39936,19 @@
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="23" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="B263" s="23" t="s">
-        <v>1794</v>
+        <v>1799</v>
       </c>
       <c r="C263" s="23" t="s">
-        <v>1795</v>
+        <v>1800</v>
       </c>
       <c r="D263" s="23" t="s">
         <v>1295</v>
       </c>
       <c r="E263" s="23" t="s">
-        <v>356</v>
+        <v>1317</v>
       </c>
       <c r="F263" s="23" t="s">
         <v>44</v>
@@ -39914,34 +39964,42 @@
         <v>436</v>
       </c>
       <c r="K263" s="23" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="L263" s="23" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="M263" s="23" t="n">
         <v>4</v>
       </c>
       <c r="N263" s="23"/>
-      <c r="O263" s="23"/>
-      <c r="P263" s="23"/>
+      <c r="O263" s="23" t="s">
+        <v>1290</v>
+      </c>
+      <c r="P263" s="23" t="s">
+        <v>1801</v>
+      </c>
       <c r="Q263" s="23"/>
-      <c r="R263" s="23"/>
-      <c r="S263" s="23"/>
+      <c r="R263" s="23" t="s">
+        <v>1096</v>
+      </c>
+      <c r="S263" s="23" t="s">
+        <v>131</v>
+      </c>
       <c r="T263" s="23" t="s">
-        <v>135</v>
+        <v>68</v>
       </c>
       <c r="U263" s="23" t="s">
-        <v>467</v>
+        <v>1097</v>
       </c>
       <c r="V263" s="23" t="n">
         <v>0</v>
       </c>
       <c r="W263" s="23" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="X263" s="23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y263" s="23" t="n">
         <v>0</v>
@@ -39956,18 +40014,18 @@
         <v>0</v>
       </c>
       <c r="AC263" s="23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="23" t="s">
-        <v>1796</v>
+        <v>1802</v>
       </c>
       <c r="B264" s="23" t="s">
-        <v>1797</v>
+        <v>1803</v>
       </c>
       <c r="C264" s="23" t="s">
-        <v>1798</v>
+        <v>1804</v>
       </c>
       <c r="D264" s="23" t="s">
         <v>1295</v>
@@ -39995,11 +40053,11 @@
         <v>460</v>
       </c>
       <c r="M264" s="23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N264" s="23"/>
       <c r="O264" s="23" t="s">
-        <v>1799</v>
+        <v>790</v>
       </c>
       <c r="P264" s="23"/>
       <c r="Q264" s="23"/>
@@ -40025,23 +40083,179 @@
         <v>0</v>
       </c>
       <c r="Y264" s="23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Z264" s="23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA264" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB264" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC264" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A265" s="23" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B265" s="23" t="s">
+        <v>1806</v>
+      </c>
+      <c r="C265" s="23" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D265" s="23" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E265" s="23" t="s">
+        <v>356</v>
+      </c>
+      <c r="F265" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="G265" s="23"/>
+      <c r="H265" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="I265" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="J265" s="23" t="s">
+        <v>436</v>
+      </c>
+      <c r="K265" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="L265" s="23" t="s">
+        <v>466</v>
+      </c>
+      <c r="M265" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="N265" s="23"/>
+      <c r="O265" s="23"/>
+      <c r="P265" s="23"/>
+      <c r="Q265" s="23"/>
+      <c r="R265" s="23"/>
+      <c r="S265" s="23"/>
+      <c r="T265" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="U265" s="23" t="s">
+        <v>467</v>
+      </c>
+      <c r="V265" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W265" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X265" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y265" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z265" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA265" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB265" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC265" s="23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A266" s="23" t="s">
+        <v>1808</v>
+      </c>
+      <c r="B266" s="23" t="s">
+        <v>1809</v>
+      </c>
+      <c r="C266" s="23" t="s">
+        <v>1810</v>
+      </c>
+      <c r="D266" s="23" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E266" s="23" t="s">
+        <v>356</v>
+      </c>
+      <c r="F266" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="G266" s="23"/>
+      <c r="H266" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="I266" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="J266" s="23" t="s">
+        <v>436</v>
+      </c>
+      <c r="K266" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="L266" s="23" t="s">
+        <v>460</v>
+      </c>
+      <c r="M266" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="N266" s="23"/>
+      <c r="O266" s="23" t="s">
+        <v>1811</v>
+      </c>
+      <c r="P266" s="23"/>
+      <c r="Q266" s="23"/>
+      <c r="R266" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="S266" s="23" t="s">
+        <v>365</v>
+      </c>
+      <c r="T266" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="U266" s="23" t="s">
+        <v>462</v>
+      </c>
+      <c r="V266" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W266" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X266" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y266" s="23" t="n">
         <v>2.6</v>
       </c>
-      <c r="Z264" s="23" t="n">
+      <c r="Z266" s="23" t="n">
         <v>0.4</v>
       </c>
-      <c r="AA264" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB264" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC264" s="23" t="n">
+      <c r="AA266" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB266" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC266" s="23" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC264"/>
+  <autoFilter ref="A1:AC266"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -40067,55 +40281,55 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1800</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1801</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>1802</v>
+        <v>1814</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1803</v>
+        <v>1815</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1804</v>
+        <v>1816</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>1805</v>
+        <v>1817</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>1806</v>
+        <v>1818</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>1807</v>
+        <v>1819</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>1808</v>
+        <v>1820</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>1809</v>
+        <v>1821</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>1810</v>
+        <v>1822</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>1811</v>
+        <v>1823</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>1812</v>
+        <v>1824</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>1813</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>1814</v>
+        <v>1826</v>
       </c>
       <c r="B5" s="12" t="n">
         <v>224</v>
@@ -40154,7 +40368,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>1815</v>
+        <v>1827</v>
       </c>
       <c r="B6" s="12" t="n">
         <v>229</v>
@@ -40193,7 +40407,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>1816</v>
+        <v>1828</v>
       </c>
       <c r="B7" s="12" t="n">
         <v>225</v>
@@ -40232,7 +40446,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>1817</v>
+        <v>1829</v>
       </c>
       <c r="B8" s="12" t="n">
         <v>368</v>
@@ -40256,10 +40470,10 @@
         <v>41</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J8" s="12" t="n">
-        <v>578</v>
+        <v>592</v>
       </c>
       <c r="K8" s="12" t="n">
         <v>1177</v>
@@ -40271,7 +40485,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>1818</v>
+        <v>1830</v>
       </c>
       <c r="B9" s="12" t="n">
         <v>402</v>
@@ -40310,7 +40524,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>1819</v>
+        <v>1831</v>
       </c>
       <c r="B10" s="12" t="n">
         <v>182</v>
@@ -40349,7 +40563,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>1820</v>
+        <v>1832</v>
       </c>
       <c r="B11" s="12" t="n">
         <v>184</v>
@@ -40373,10 +40587,10 @@
         <v>49</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>576</v>
+        <v>586</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>928</v>
@@ -40388,7 +40602,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>1821</v>
+        <v>1833</v>
       </c>
       <c r="B12" s="12" t="n">
         <v>183</v>
@@ -40427,7 +40641,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>1822</v>
+        <v>1834</v>
       </c>
       <c r="B13" s="12" t="n">
         <v>106</v>
@@ -40466,7 +40680,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>1823</v>
+        <v>1835</v>
       </c>
       <c r="B14" s="15" t="n">
         <f aca="false">SUM(B5:B12)</f>
@@ -40498,11 +40712,11 @@
       </c>
       <c r="I14" s="15" t="n">
         <f aca="false">SUM(I5:I12)</f>
-        <v>833</v>
+        <v>809</v>
       </c>
       <c r="J14" s="15" t="n">
         <f aca="false">SUM(J5:J12)</f>
-        <v>4882</v>
+        <v>4906</v>
       </c>
       <c r="K14" s="15" t="n">
         <f aca="false">SUM(K5:K12)</f>
@@ -40515,25 +40729,25 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>1824</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>1825</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>1826</v>
+        <v>1838</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>1827</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>1828</v>
+        <v>1840</v>
       </c>
       <c r="B19" s="7" t="n">
         <f aca="false">AVERAGE(B10:B12)</f>
@@ -40542,7 +40756,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>1829</v>
+        <v>1841</v>
       </c>
       <c r="B20" s="7" t="n">
         <f aca="false">AVERAGE(G10:G12)</f>
@@ -40551,7 +40765,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>1830</v>
+        <v>1842</v>
       </c>
       <c r="B21" s="25" t="n">
         <v>0.73</v>
@@ -40559,7 +40773,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>1831</v>
+        <v>1843</v>
       </c>
       <c r="B22" s="7" t="n">
         <f aca="false">(B19+B20)*B21</f>
@@ -40568,7 +40782,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>1832</v>
+        <v>1844</v>
       </c>
       <c r="B23" s="8" t="n">
         <f aca="false">(DATE(2027,1,1)-DATE(2026,10,8))/365</f>
@@ -40577,7 +40791,7 @@
     </row>
     <row r="24" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="26" t="s">
-        <v>1833</v>
+        <v>1845</v>
       </c>
       <c r="B24" s="26"/>
       <c r="C24" s="26"/>
@@ -40593,7 +40807,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>1834</v>
+        <v>1846</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>55</v>
@@ -40614,12 +40828,12 @@
         <v>60</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>1835</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>1836</v>
+        <v>1848</v>
       </c>
       <c r="B27" s="12" t="n">
         <f aca="false">B22*B23</f>
@@ -40651,119 +40865,137 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>1837</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>1838</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>1839</v>
+        <v>1851</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>1840</v>
+        <v>1852</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>1841</v>
+        <v>1853</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>1842</v>
+        <v>1854</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>1843</v>
+        <v>1855</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>1856</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>1844</v>
+        <v>1857</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>1845</v>
+        <v>1858</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>1846</v>
+        <v>1859</v>
       </c>
       <c r="D32" s="12" t="n">
         <v>57</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>1847</v>
+        <v>1860</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>1861</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>1848</v>
+        <v>1862</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>1849</v>
+        <v>1863</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>1850</v>
+        <v>1864</v>
       </c>
       <c r="D33" s="12" t="n">
         <v>40</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>1851</v>
+        <v>1865</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>1866</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>1852</v>
+        <v>1867</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>1853</v>
+        <v>1868</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>1854</v>
+        <v>1869</v>
       </c>
       <c r="D34" s="12" t="n">
         <v>35</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>1855</v>
+        <v>1870</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>1871</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="s">
-        <v>1856</v>
+        <v>1872</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>1857</v>
+        <v>1480</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>1858</v>
+        <v>1873</v>
       </c>
       <c r="D35" s="12" t="n">
         <v>14</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>1859</v>
+        <v>1874</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>1875</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>1860</v>
+        <v>1876</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>1861</v>
+        <v>1515</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>1862</v>
+        <v>1877</v>
       </c>
       <c r="D36" s="12" t="n">
         <v>10</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>1863</v>
+        <v>1878</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>1879</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="s">
-        <v>1864</v>
+        <v>1880</v>
       </c>
     </row>
   </sheetData>
@@ -40798,15 +41030,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1865</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="27" t="s">
-        <v>1866</v>
+        <v>1882</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>1867</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40814,15 +41046,15 @@
         <v>22</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>1868</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1869</v>
+        <v>1885</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>1870</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40830,7 +41062,7 @@
         <v>34</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>1871</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40838,7 +41070,7 @@
         <v>26</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>1872</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40846,31 +41078,31 @@
         <v>46</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>1873</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>1874</v>
+        <v>1890</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>1875</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>1876</v>
+        <v>1892</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>1877</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>1878</v>
+        <v>1894</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>1879</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40878,48 +41110,48 @@
         <v>135</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>1880</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>1881</v>
+        <v>1897</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>1882</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="27" t="s">
-        <v>1883</v>
+        <v>1899</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>1884</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>1885</v>
+        <v>1901</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1886</v>
+        <v>1902</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>1887</v>
+        <v>1903</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>1888</v>
+        <v>1904</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>1887</v>
+        <v>1903</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>1889</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="29" t="s">
-        <v>1890</v>
+        <v>1906</v>
       </c>
       <c r="B17" s="29" t="n">
         <v>1.28</v>
@@ -40939,7 +41171,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="29" t="s">
-        <v>1891</v>
+        <v>1907</v>
       </c>
       <c r="B18" s="29" t="n">
         <v>1.39</v>
@@ -40959,7 +41191,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="29" t="s">
-        <v>1892</v>
+        <v>1908</v>
       </c>
       <c r="B19" s="29" t="n">
         <v>1.62</v>
@@ -40979,7 +41211,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="29" t="s">
-        <v>1893</v>
+        <v>1909</v>
       </c>
       <c r="B20" s="29" t="n">
         <v>1.13</v>
@@ -40999,7 +41231,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="29" t="s">
-        <v>1894</v>
+        <v>1910</v>
       </c>
       <c r="B21" s="29" t="n">
         <v>1.72</v>
@@ -41019,7 +41251,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>1895</v>
+        <v>1911</v>
       </c>
     </row>
   </sheetData>
